--- a/2026/BELGRANO 1646/Junio/Junio-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Junio/Junio-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB214C37-AABA-484F-BD6E-333F82687568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9B9445-F537-4846-8E86-ABB17020302D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$126</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="141">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -425,85 +425,67 @@
     <t>BORRAR A MAURO MARANTE DE MAILS</t>
   </si>
   <si>
-    <t>Debito 13/04</t>
-  </si>
-  <si>
-    <t>VTO: 18/06</t>
-  </si>
-  <si>
-    <t>PERÍODO: MAYO</t>
-  </si>
-  <si>
-    <t>Honorarios MAYO</t>
-  </si>
-  <si>
-    <t>Energroup - SERVICE DE MANTENIMIENTO PREVENTIVO - MAYO</t>
-  </si>
-  <si>
-    <t>Fumigacion - Mes de MAYO</t>
-  </si>
-  <si>
-    <t>Mes de ABRIL</t>
-  </si>
-  <si>
-    <t>MP:1148 - Mes de ABRIL - Se adeuda MAYO</t>
-  </si>
-  <si>
-    <t>Ingreso mes de ABRIL</t>
-  </si>
-  <si>
-    <t>Cortinas metalicas - Cambio de soporte izquierdo, cojinete ruleman y punta de eje, cambio de fletes, nivelacion de paño metalico y lubricacion de persiana metalica en primer y segundo piso</t>
-  </si>
-  <si>
-    <t>Servisur - Reloj timer, iluminacion y reconeccion de circuito toma corriente - Lamparitas en apliques de terraza</t>
-  </si>
-  <si>
-    <t>Casa Ruan - Lamparas y reloj</t>
-  </si>
-  <si>
-    <t>Debito 05/05</t>
-  </si>
-  <si>
-    <t>Julio Doartero - Cambio de automatico, mano de obra y materiales</t>
-  </si>
-  <si>
-    <t>SA Seguridad - Servicio realizado por sistema CCTV de camaras de seguridad</t>
-  </si>
-  <si>
-    <t>Contessi - Reparacion de tensor trasero izquierdo de cabina de montacoches</t>
-  </si>
-  <si>
-    <t>Urbeco - limpieza y desinfecion de tanques de agua potable, analisis y certificado corrrespondiente</t>
-  </si>
-  <si>
-    <t>Servisur - Plafones de 12w en escaleras y lamparas en hall de entrada</t>
-  </si>
-  <si>
-    <t>Casa Ruan - Compra de materiales electricos</t>
-  </si>
-  <si>
-    <t>Pago mis cuentas 06/05</t>
-  </si>
-  <si>
     <t>Alterini Guido - Mantenimiento jardineria</t>
   </si>
   <si>
-    <t>Debito 22/05</t>
-  </si>
-  <si>
     <t>Articulos de limpieza - Para pileta</t>
   </si>
   <si>
     <t xml:space="preserve">Articulos de limpieza </t>
   </si>
   <si>
-    <t>SA Seguridad - Emergencia porton rejas</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>SGP colocacion de 4 cajas de paso en empalmes de luces de cantero patio SUM</t>
+    <t>VTO: 17/07</t>
+  </si>
+  <si>
+    <t>PERÍODO: JUNIO</t>
+  </si>
+  <si>
+    <t>Fumigacion - Mes de JUNIO</t>
+  </si>
+  <si>
+    <t>Mes de MAYO</t>
+  </si>
+  <si>
+    <t>MP:1148 - Mes de MAYO - Se adeuda JUNIO</t>
+  </si>
+  <si>
+    <t>Ingreso mes de MAYO</t>
+  </si>
+  <si>
+    <t>Servisur - Reloj timer y programacion - 2 plafones externos de 12w</t>
+  </si>
+  <si>
+    <t>Matafuegos FIRE - Compra de uniformes Sr. Encargado</t>
+  </si>
+  <si>
+    <t>Cerrajeria - Servicio de cerrajeria sobre control de acceso</t>
+  </si>
+  <si>
+    <t>Julio Doartero - Emergencia electrica</t>
+  </si>
+  <si>
+    <t>Honorarios JUNIO + SAC</t>
+  </si>
+  <si>
+    <t>Energroup - No llego la boleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Alejo Simonassi </t>
+  </si>
+  <si>
+    <t>Sra. Abogada Edith Bragonzi (Abogada Sr Simonassi)</t>
+  </si>
+  <si>
+    <t>Sr. Servian Cesar - Mediador</t>
+  </si>
+  <si>
+    <t>Sr. Gabriel Villegas - Abogado Consorcio</t>
+  </si>
+  <si>
+    <t>Entendiendo que en su momento, se le habia cobrado al Sr. Simonassi $3.000.000, la diferencia entre lo gastado ($6.484.614,10) y el monto mencionado se prorrateara como extraordinario en los proximos dos meses ($1.742.307)</t>
+  </si>
+  <si>
+    <t>Gasto abonado por Sr. Nestor Campana : Reparación de superficie dañada por filtración y pintura en dormitorio con materiales incluídos.</t>
   </si>
 </sst>
 </file>
@@ -520,7 +502,7 @@
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -681,6 +663,14 @@
       <i/>
       <u/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1085,7 +1075,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1287,6 +1277,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1376,78 +1372,85 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1847,7 +1850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N134"/>
+  <dimension ref="A1:N136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -1866,13 +1869,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="90"/>
-      <c r="B1" s="155" t="s">
+      <c r="B1" s="157" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="156"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="158"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
@@ -1909,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="106" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C5" s="106" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D5" s="106"/>
       <c r="E5" s="106"/>
@@ -1976,29 +1979,29 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="78"/>
-      <c r="B14" s="159" t="s">
+      <c r="B14" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="160"/>
-      <c r="D14" s="161"/>
+      <c r="C14" s="162"/>
+      <c r="D14" s="163"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="78"/>
-      <c r="B15" s="162"/>
-      <c r="C15" s="163"/>
-      <c r="D15" s="164"/>
+      <c r="B15" s="164"/>
+      <c r="C15" s="165"/>
+      <c r="D15" s="166"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="78"/>
-      <c r="B16" s="162"/>
-      <c r="C16" s="163"/>
-      <c r="D16" s="164"/>
+      <c r="B16" s="164"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="166"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="78"/>
-      <c r="B17" s="165"/>
-      <c r="C17" s="166"/>
-      <c r="D17" s="167"/>
+      <c r="B17" s="167"/>
+      <c r="C17" s="168"/>
+      <c r="D17" s="169"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="78"/>
@@ -2037,7 +2040,7 @@
         <v>107</v>
       </c>
       <c r="B22" s="79" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C22" s="79"/>
       <c r="D22" s="150"/>
@@ -2051,15 +2054,15 @@
       <c r="B23" s="79"/>
       <c r="C23" s="79"/>
       <c r="D23" s="102">
-        <v>1575703.3</v>
+        <v>2640801.16</v>
       </c>
       <c r="E23" s="49">
         <f>D23*91.91%</f>
-        <v>1448228.9030299999</v>
+        <v>2427160.3461559997</v>
       </c>
       <c r="F23" s="49">
         <f>D23*8.09%</f>
-        <v>127474.39697</v>
+        <v>213640.81384400002</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -2069,15 +2072,15 @@
       <c r="B24" s="79"/>
       <c r="C24" s="79"/>
       <c r="D24" s="102">
-        <v>-342715.56</v>
+        <v>-574674.24</v>
       </c>
       <c r="E24" s="49">
         <f t="shared" ref="E24:E26" si="0">D24*91.91%</f>
-        <v>-314989.87119599996</v>
+        <v>-528183.09398399992</v>
       </c>
       <c r="F24" s="49">
         <f t="shared" ref="F24:F26" si="1">D24*8.09%</f>
-        <v>-27725.688804000001</v>
+        <v>-46491.146015999999</v>
       </c>
       <c r="G24" s="34"/>
     </row>
@@ -2088,15 +2091,15 @@
       <c r="B25" s="79"/>
       <c r="C25" s="79"/>
       <c r="D25" s="102">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E25" s="49">
         <f t="shared" si="0"/>
-        <v>0.14705599999999999</v>
+        <v>7.3527999999999996E-2</v>
       </c>
       <c r="F25" s="49">
         <f t="shared" si="1"/>
-        <v>1.2944000000000001E-2</v>
+        <v>6.4720000000000003E-3</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -2113,7 +2116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="118" t="s">
         <v>3</v>
       </c>
@@ -2121,19 +2124,19 @@
       <c r="C27" s="118"/>
       <c r="D27" s="33">
         <f>SUM(D23:D26)</f>
-        <v>1232987.8999999999</v>
+        <v>2066127.0000000002</v>
       </c>
       <c r="E27" s="33">
         <f>SUM(E23:E26)</f>
-        <v>1133239.1788900001</v>
+        <v>1898977.3256999997</v>
       </c>
       <c r="F27" s="33">
         <f>SUM(F23:F26)</f>
-        <v>99748.721109999999</v>
+        <v>167149.67430000004</v>
       </c>
       <c r="G27" s="34">
         <f>E27+F27</f>
-        <v>1232987.9000000001</v>
+        <v>2066126.9999999998</v>
       </c>
       <c r="H27" s="61" t="str">
         <f>IF(D27=G27, "", "Error")</f>
@@ -2221,7 +2224,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="119"/>
       <c r="B33" s="79"/>
       <c r="C33" s="79"/>
@@ -2236,7 +2239,7 @@
       </c>
       <c r="H33" s="61"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="79"/>
       <c r="B34" s="79"/>
       <c r="C34" s="79"/>
@@ -2251,7 +2254,7 @@
       </c>
       <c r="H34" s="61"/>
     </row>
-    <row r="35" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="119"/>
       <c r="B35" s="79"/>
       <c r="C35" s="79"/>
@@ -2266,7 +2269,7 @@
       </c>
       <c r="H35" s="61"/>
     </row>
-    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="118" t="s">
         <v>97</v>
       </c>
@@ -2374,7 +2377,7 @@
       </c>
       <c r="B43" s="79"/>
       <c r="C43" s="79"/>
-      <c r="D43" s="104"/>
+      <c r="D43" s="37"/>
       <c r="E43" s="38"/>
       <c r="F43" s="26"/>
       <c r="H43" s="61"/>
@@ -2402,21 +2405,19 @@
       <c r="A45" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="79" t="s">
-        <v>120</v>
-      </c>
+      <c r="B45" s="79"/>
       <c r="C45" s="79"/>
       <c r="D45" s="37">
-        <f>75057.3+8339.7+151650.1</f>
-        <v>235047.1</v>
+        <f>70906.65+7878.52+147382.7</f>
+        <v>226167.87</v>
       </c>
       <c r="E45" s="49">
         <f>D45*91.91%</f>
-        <v>216031.78960999998</v>
+        <v>207870.88931699996</v>
       </c>
       <c r="F45" s="49">
         <f>D45*8.09%</f>
-        <v>19015.310389999999</v>
+        <v>18296.980682999998</v>
       </c>
       <c r="H45" s="61"/>
     </row>
@@ -2424,20 +2425,18 @@
       <c r="A46" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="B46" s="101" t="s">
-        <v>139</v>
-      </c>
+      <c r="B46" s="101"/>
       <c r="C46" s="79"/>
       <c r="D46" s="37">
-        <v>739569.96</v>
+        <v>698662.43</v>
       </c>
       <c r="E46" s="49">
         <f>D46*91.91%</f>
-        <v>679738.75023599993</v>
+        <v>642140.63941299997</v>
       </c>
       <c r="F46" s="49">
         <f>D46*8.09%</f>
-        <v>59831.209763999999</v>
+        <v>56521.790587000003</v>
       </c>
       <c r="H46" s="61"/>
     </row>
@@ -2449,19 +2448,19 @@
       <c r="C47" s="122"/>
       <c r="D47" s="33">
         <f>SUM(D44:D46)</f>
-        <v>981259.05999999994</v>
+        <v>931472.3</v>
       </c>
       <c r="E47" s="33">
         <f t="shared" ref="E47:F47" si="6">SUM(E44:E46)</f>
-        <v>901875.20204599993</v>
+        <v>856116.19092999992</v>
       </c>
       <c r="F47" s="33">
         <f t="shared" si="6"/>
-        <v>79383.857954000006</v>
+        <v>75356.109070000006</v>
       </c>
       <c r="G47" s="34">
         <f>E47+F47</f>
-        <v>981259.05999999994</v>
+        <v>931472.29999999993</v>
       </c>
       <c r="H47" s="61" t="str">
         <f>IF(D47=G47, "", "Error")</f>
@@ -2507,1327 +2506,1313 @@
       </c>
       <c r="J49" s="76"/>
     </row>
-    <row r="50" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="123" t="s">
-        <v>135</v>
-      </c>
-      <c r="B50" s="79"/>
+    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="117" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="126"/>
       <c r="C50" s="79"/>
       <c r="D50" s="37">
-        <v>380000</v>
+        <v>0</v>
       </c>
       <c r="E50" s="60">
-        <f>D50</f>
-        <v>380000</v>
-      </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="67"/>
+        <f t="shared" ref="E50:E55" si="7">D50*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="49">
+        <f t="shared" ref="F50:F55" si="8">D50*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="34">
+        <f t="shared" ref="G50:G52" si="9">D50</f>
+        <v>0</v>
+      </c>
+      <c r="H50" s="67">
+        <f t="shared" ref="H50:H52" si="10">E50+F50</f>
+        <v>0</v>
+      </c>
       <c r="I50" s="76"/>
       <c r="J50" s="76"/>
     </row>
-    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="117" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" s="126"/>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="79"/>
       <c r="C51" s="79"/>
       <c r="D51" s="37">
-        <v>255779</v>
+        <v>45000</v>
       </c>
       <c r="E51" s="60">
-        <f t="shared" ref="E51:E58" si="7">D51*91.91%</f>
-        <v>235086.47889999999</v>
+        <f>D51</f>
+        <v>45000</v>
       </c>
       <c r="F51" s="49">
-        <f t="shared" ref="F51:F58" si="8">D51*8.09%</f>
-        <v>20692.521099999998</v>
+        <v>0</v>
       </c>
       <c r="G51" s="34">
-        <f t="shared" ref="G51:G69" si="9">D51</f>
-        <v>255779</v>
+        <f t="shared" si="9"/>
+        <v>45000</v>
       </c>
       <c r="H51" s="67">
-        <f t="shared" ref="H51:H69" si="10">E51+F51</f>
-        <v>255779</v>
+        <f t="shared" si="10"/>
+        <v>45000</v>
       </c>
       <c r="I51" s="76"/>
       <c r="J51" s="76"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="119" t="s">
         <v>134</v>
       </c>
       <c r="B52" s="79"/>
       <c r="C52" s="79"/>
       <c r="D52" s="37">
-        <v>59169</v>
+        <v>0</v>
       </c>
       <c r="E52" s="60">
-        <f>D52</f>
-        <v>59169</v>
+        <f t="shared" ref="E52" si="11">D52*91.91%</f>
+        <v>0</v>
       </c>
       <c r="F52" s="49">
+        <f t="shared" ref="F52" si="12">D52*8.09%</f>
         <v>0</v>
       </c>
       <c r="G52" s="34">
         <f t="shared" si="9"/>
-        <v>59169</v>
+        <v>0</v>
       </c>
       <c r="H52" s="67">
         <f t="shared" si="10"/>
-        <v>59169</v>
+        <v>0</v>
       </c>
       <c r="I52" s="76"/>
       <c r="J52" s="76"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="79" t="s">
-        <v>144</v>
-      </c>
-      <c r="B53" s="79"/>
+      <c r="A53" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="79" t="s">
+        <v>109</v>
+      </c>
       <c r="C53" s="79"/>
       <c r="D53" s="37">
-        <v>108900</v>
+        <v>173191</v>
       </c>
       <c r="E53" s="60">
-        <f>D53</f>
-        <v>108900</v>
+        <f>D53*91.91%</f>
+        <v>159179.84809999997</v>
       </c>
       <c r="F53" s="49">
-        <v>0</v>
-      </c>
-      <c r="G53" s="34"/>
-      <c r="H53" s="67"/>
-      <c r="I53" s="76"/>
-      <c r="J53" s="76"/>
+        <f t="shared" si="8"/>
+        <v>14011.151900000001</v>
+      </c>
+      <c r="G53" s="34">
+        <f t="shared" ref="G53:G65" si="13">D53</f>
+        <v>173191</v>
+      </c>
+      <c r="H53" s="67">
+        <f>E53+F53</f>
+        <v>173190.99999999997</v>
+      </c>
+      <c r="I53" s="76">
+        <f t="shared" ref="I53:I65" si="14">H53-D53</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="76">
+        <f t="shared" ref="J53:J65" si="15">G53-D53</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="119" t="s">
-        <v>124</v>
-      </c>
-      <c r="B54" s="79"/>
+        <v>11</v>
+      </c>
+      <c r="B54" s="101"/>
       <c r="C54" s="79"/>
       <c r="D54" s="37">
-        <v>205404</v>
+        <v>515749.86</v>
       </c>
       <c r="E54" s="60">
-        <f t="shared" ref="E54" si="11">D54*91.91%</f>
-        <v>188786.81639999998</v>
+        <f t="shared" si="7"/>
+        <v>474025.69632599992</v>
       </c>
       <c r="F54" s="49">
-        <f t="shared" ref="F54" si="12">D54*8.09%</f>
-        <v>16617.1836</v>
+        <f t="shared" si="8"/>
+        <v>41724.163673999996</v>
       </c>
       <c r="G54" s="34">
-        <f t="shared" ref="G54" si="13">D54</f>
-        <v>205404</v>
+        <f t="shared" si="13"/>
+        <v>515749.86</v>
       </c>
       <c r="H54" s="67">
-        <f t="shared" ref="H54" si="14">E54+F54</f>
-        <v>205403.99999999997</v>
-      </c>
-      <c r="I54" s="76"/>
-      <c r="J54" s="76"/>
+        <f t="shared" ref="H54:H65" si="16">E54+F54</f>
+        <v>515749.85999999993</v>
+      </c>
+      <c r="I54" s="76">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="76">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="119" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" s="79" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="79" t="s">
-        <v>141</v>
-      </c>
+      <c r="A55" s="120" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" s="101"/>
+      <c r="C55" s="101"/>
       <c r="D55" s="37">
-        <v>129315.21</v>
+        <v>1425373.94</v>
       </c>
       <c r="E55" s="60">
-        <f>D55*91.91%</f>
-        <v>118853.609511</v>
+        <f t="shared" si="7"/>
+        <v>1310061.1882539999</v>
       </c>
       <c r="F55" s="49">
         <f t="shared" si="8"/>
-        <v>10461.600489</v>
+        <v>115312.75174599999</v>
       </c>
       <c r="G55" s="34">
-        <f t="shared" si="9"/>
-        <v>129315.21</v>
+        <f t="shared" si="13"/>
+        <v>1425373.94</v>
       </c>
       <c r="H55" s="67">
-        <f>E55+F55</f>
-        <v>129315.21</v>
+        <f t="shared" si="16"/>
+        <v>1425373.94</v>
       </c>
       <c r="I55" s="76">
-        <f t="shared" ref="I55:I69" si="15">H55-D55</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J55" s="76">
-        <f t="shared" ref="J55:J69" si="16">G55-D55</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="119" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="101" t="s">
+      <c r="A56" s="120" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="140"/>
+      <c r="C56" s="152"/>
+      <c r="D56" s="37">
+        <v>1237365.1000000001</v>
+      </c>
+      <c r="E56" s="60">
+        <f>D56</f>
+        <v>1237365.1000000001</v>
+      </c>
+      <c r="F56" s="49">
+        <v>0</v>
+      </c>
+      <c r="G56" s="34">
+        <f t="shared" si="13"/>
+        <v>1237365.1000000001</v>
+      </c>
+      <c r="H56" s="67">
+        <f t="shared" si="16"/>
+        <v>1237365.1000000001</v>
+      </c>
+      <c r="I56" s="76"/>
+      <c r="J56" s="76"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="127" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="141"/>
+      <c r="C57" s="142"/>
+      <c r="D57" s="37">
+        <v>63300</v>
+      </c>
+      <c r="E57" s="60">
+        <f t="shared" ref="E57:E58" si="17">D57</f>
+        <v>63300</v>
+      </c>
+      <c r="F57" s="49"/>
+      <c r="G57" s="34">
+        <f t="shared" si="13"/>
+        <v>63300</v>
+      </c>
+      <c r="H57" s="67">
+        <f t="shared" si="16"/>
+        <v>63300</v>
+      </c>
+      <c r="I57" s="76"/>
+      <c r="J57" s="76">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="151" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" s="141"/>
+      <c r="C58" s="142"/>
+      <c r="D58" s="37">
+        <v>237000</v>
+      </c>
+      <c r="E58" s="60">
+        <f t="shared" si="17"/>
+        <v>237000</v>
+      </c>
+      <c r="F58" s="49"/>
+      <c r="G58" s="34">
+        <f t="shared" si="13"/>
+        <v>237000</v>
+      </c>
+      <c r="H58" s="67">
+        <f t="shared" si="16"/>
+        <v>237000</v>
+      </c>
+      <c r="I58" s="76"/>
+      <c r="J58" s="76"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="153" t="s">
         <v>132</v>
       </c>
-      <c r="C56" s="79"/>
-      <c r="D56" s="37">
-        <v>353513.62</v>
-      </c>
-      <c r="E56" s="60">
-        <f t="shared" si="7"/>
-        <v>324914.36814199999</v>
-      </c>
-      <c r="F56" s="49">
-        <f t="shared" si="8"/>
-        <v>28599.251858</v>
-      </c>
-      <c r="G56" s="34">
-        <f t="shared" si="9"/>
-        <v>353513.62</v>
-      </c>
-      <c r="H56" s="67">
-        <f t="shared" si="10"/>
-        <v>353513.62</v>
-      </c>
-      <c r="I56" s="76">
+      <c r="B59" s="128"/>
+      <c r="C59" s="129"/>
+      <c r="D59" s="37">
+        <v>85000</v>
+      </c>
+      <c r="E59" s="60">
+        <f t="shared" ref="E59" si="18">D59*91.91%</f>
+        <v>78123.5</v>
+      </c>
+      <c r="F59" s="49">
+        <f t="shared" ref="F59" si="19">D59*8.09%</f>
+        <v>6876.5</v>
+      </c>
+      <c r="G59" s="34">
+        <f t="shared" si="13"/>
+        <v>85000</v>
+      </c>
+      <c r="H59" s="67">
+        <f t="shared" si="16"/>
+        <v>85000</v>
+      </c>
+      <c r="I59" s="76">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="76">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J56" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="119" t="s">
-        <v>136</v>
-      </c>
-      <c r="B57" s="79"/>
-      <c r="C57" s="79"/>
-      <c r="D57" s="37">
-        <v>544500</v>
-      </c>
-      <c r="E57" s="60">
-        <f t="shared" si="7"/>
-        <v>500449.94999999995</v>
-      </c>
-      <c r="F57" s="49">
-        <f t="shared" si="8"/>
-        <v>44050.05</v>
-      </c>
-      <c r="G57" s="34">
-        <f t="shared" si="9"/>
-        <v>544500</v>
-      </c>
-      <c r="H57" s="67">
-        <f t="shared" si="10"/>
-        <v>544500</v>
-      </c>
-      <c r="I57" s="76"/>
-      <c r="J57" s="76"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="120" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="101"/>
-      <c r="C58" s="101"/>
-      <c r="D58" s="37">
-        <v>37141.58</v>
-      </c>
-      <c r="E58" s="60">
-        <f t="shared" si="7"/>
-        <v>34136.826177999996</v>
-      </c>
-      <c r="F58" s="49">
-        <f t="shared" si="8"/>
-        <v>3004.7538220000001</v>
-      </c>
-      <c r="G58" s="34">
-        <f t="shared" si="9"/>
-        <v>37141.58</v>
-      </c>
-      <c r="H58" s="67">
-        <f t="shared" si="10"/>
-        <v>37141.579999999994</v>
-      </c>
-      <c r="I58" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="101" t="s">
-        <v>146</v>
-      </c>
-      <c r="B59" s="140"/>
-      <c r="C59" s="152"/>
-      <c r="D59" s="37">
-        <v>150000</v>
-      </c>
-      <c r="E59" s="60">
-        <f>D59</f>
-        <v>150000</v>
-      </c>
-      <c r="F59" s="49">
-        <v>0</v>
-      </c>
-      <c r="G59" s="34">
-        <f t="shared" si="9"/>
-        <v>150000</v>
-      </c>
-      <c r="H59" s="67">
-        <f t="shared" si="10"/>
-        <v>150000</v>
-      </c>
-      <c r="I59" s="76"/>
-      <c r="J59" s="76"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="127" t="s">
-        <v>125</v>
-      </c>
-      <c r="B60" s="141"/>
-      <c r="C60" s="142"/>
+    </row>
+    <row r="60" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="187" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="182"/>
+      <c r="C60" s="183"/>
       <c r="D60" s="37">
-        <v>62000</v>
+        <v>278000</v>
       </c>
       <c r="E60" s="60">
-        <f t="shared" ref="E60:E61" si="17">D60</f>
-        <v>62000</v>
+        <f>D60</f>
+        <v>278000</v>
       </c>
       <c r="F60" s="49"/>
       <c r="G60" s="34">
-        <f t="shared" si="9"/>
-        <v>62000</v>
+        <f t="shared" si="13"/>
+        <v>278000</v>
       </c>
       <c r="H60" s="67"/>
       <c r="I60" s="76"/>
-      <c r="J60" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="151" t="s">
-        <v>140</v>
-      </c>
-      <c r="B61" s="141"/>
-      <c r="C61" s="142"/>
+      <c r="J60" s="76"/>
+    </row>
+    <row r="61" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="184" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" s="185"/>
+      <c r="C61" s="186"/>
       <c r="D61" s="37">
-        <v>90000</v>
+        <v>152940</v>
       </c>
       <c r="E61" s="60">
-        <f t="shared" si="17"/>
-        <v>90000</v>
+        <f t="shared" ref="E61:E63" si="20">D61</f>
+        <v>152940</v>
       </c>
       <c r="F61" s="49"/>
       <c r="G61" s="34">
-        <f t="shared" si="9"/>
-        <v>90000</v>
-      </c>
-      <c r="H61" s="67"/>
+        <f t="shared" si="13"/>
+        <v>152940</v>
+      </c>
+      <c r="H61" s="67">
+        <f t="shared" si="16"/>
+        <v>152940</v>
+      </c>
       <c r="I61" s="76"/>
-      <c r="J61" s="76"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="153" t="s">
-        <v>133</v>
-      </c>
-      <c r="B62" s="128"/>
-      <c r="C62" s="129"/>
+      <c r="J61" s="76">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="187" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="182"/>
+      <c r="C62" s="183"/>
       <c r="D62" s="37">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="E62" s="60">
-        <f t="shared" ref="E62" si="18">D62*91.91%</f>
-        <v>50550.499999999993</v>
-      </c>
-      <c r="F62" s="49">
-        <f t="shared" ref="F62" si="19">D62*8.09%</f>
-        <v>4449.5</v>
-      </c>
+        <f t="shared" si="20"/>
+        <v>65000</v>
+      </c>
+      <c r="F62" s="49"/>
       <c r="G62" s="34">
-        <f t="shared" si="9"/>
-        <v>55000</v>
+        <f t="shared" si="13"/>
+        <v>65000</v>
       </c>
       <c r="H62" s="67">
-        <f t="shared" si="10"/>
-        <v>54999.999999999993</v>
-      </c>
-      <c r="I62" s="76">
+        <f t="shared" si="16"/>
+        <v>65000</v>
+      </c>
+      <c r="I62" s="76"/>
+      <c r="J62" s="76">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J62" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="182" t="s">
+    </row>
+    <row r="63" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="187" t="s">
         <v>129</v>
       </c>
-      <c r="B63" s="183"/>
-      <c r="C63" s="184"/>
+      <c r="B63" s="182"/>
+      <c r="C63" s="183"/>
       <c r="D63" s="37">
-        <v>420000</v>
+        <v>41000</v>
       </c>
       <c r="E63" s="60">
-        <f t="shared" ref="E63:E66" si="20">D63</f>
-        <v>420000</v>
+        <f t="shared" si="20"/>
+        <v>41000</v>
       </c>
       <c r="F63" s="49"/>
       <c r="G63" s="34">
-        <f t="shared" si="9"/>
-        <v>420000</v>
+        <f t="shared" si="13"/>
+        <v>41000</v>
       </c>
       <c r="H63" s="67">
-        <f t="shared" si="10"/>
-        <v>420000</v>
+        <f t="shared" si="16"/>
+        <v>41000</v>
       </c>
       <c r="I63" s="76"/>
       <c r="J63" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="185" t="s">
-        <v>130</v>
-      </c>
-      <c r="B64" s="180"/>
-      <c r="C64" s="181"/>
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="124" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" s="139"/>
       <c r="D64" s="37">
-        <v>90000</v>
+        <v>103395</v>
       </c>
       <c r="E64" s="60">
-        <f t="shared" si="20"/>
-        <v>90000</v>
+        <f t="shared" ref="E64:E65" si="21">D64</f>
+        <v>103395</v>
       </c>
       <c r="F64" s="49"/>
       <c r="G64" s="34">
-        <f t="shared" si="9"/>
-        <v>90000</v>
+        <f t="shared" si="13"/>
+        <v>103395</v>
       </c>
       <c r="H64" s="67">
-        <f t="shared" si="10"/>
-        <v>90000</v>
-      </c>
-      <c r="I64" s="76"/>
+        <f t="shared" si="16"/>
+        <v>103395</v>
+      </c>
+      <c r="I64" s="76">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="J64" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="185" t="s">
-        <v>137</v>
-      </c>
-      <c r="B65" s="180"/>
-      <c r="C65" s="181"/>
-      <c r="D65" s="37">
-        <v>70000</v>
-      </c>
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="181"/>
+      <c r="B65" s="182"/>
+      <c r="C65" s="183"/>
+      <c r="D65" s="37"/>
       <c r="E65" s="60">
-        <f t="shared" si="20"/>
-        <v>70000</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="F65" s="49"/>
       <c r="G65" s="34">
-        <f t="shared" si="9"/>
-        <v>70000</v>
-      </c>
-      <c r="H65" s="67"/>
-      <c r="I65" s="76"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H65" s="67">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="76">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="J65" s="76">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="182" t="s">
-        <v>131</v>
-      </c>
-      <c r="B66" s="183"/>
-      <c r="C66" s="184"/>
-      <c r="D66" s="37">
-        <v>33000</v>
-      </c>
-      <c r="E66" s="60">
-        <f t="shared" si="20"/>
-        <v>33000</v>
-      </c>
-      <c r="F66" s="49">
-        <v>0</v>
+      <c r="A66" s="118" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" s="122"/>
+      <c r="C66" s="122"/>
+      <c r="D66" s="33">
+        <f>SUM(D49:D65)</f>
+        <v>4856314.9000000004</v>
+      </c>
+      <c r="E66" s="33">
+        <f>SUM(E49:E65)</f>
+        <v>4678390.33268</v>
+      </c>
+      <c r="F66" s="33">
+        <f>SUM(F49:F65)</f>
+        <v>177924.56731999997</v>
       </c>
       <c r="G66" s="34">
-        <f t="shared" ref="G66" si="21">D66</f>
-        <v>33000</v>
-      </c>
-      <c r="H66" s="67">
-        <f t="shared" ref="H66" si="22">E66+F66</f>
-        <v>33000</v>
-      </c>
-      <c r="I66" s="76"/>
-      <c r="J66" s="76"/>
-    </row>
-    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="182" t="s">
-        <v>138</v>
-      </c>
-      <c r="B67" s="183"/>
-      <c r="C67" s="184"/>
-      <c r="D67" s="37">
-        <v>25200</v>
-      </c>
-      <c r="E67" s="60">
-        <f t="shared" ref="E67:E69" si="23">D67</f>
-        <v>25200</v>
-      </c>
-      <c r="F67" s="49"/>
-      <c r="G67" s="34">
-        <f t="shared" si="9"/>
-        <v>25200</v>
-      </c>
-      <c r="H67" s="67">
-        <f t="shared" si="10"/>
-        <v>25200</v>
-      </c>
-      <c r="I67" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="B68" s="124" t="s">
-        <v>126</v>
-      </c>
-      <c r="C68" s="139"/>
-      <c r="D68" s="37">
-        <v>103395</v>
-      </c>
-      <c r="E68" s="60">
-        <f t="shared" si="23"/>
-        <v>103395</v>
-      </c>
-      <c r="F68" s="49"/>
-      <c r="G68" s="34">
-        <f t="shared" si="9"/>
-        <v>103395</v>
-      </c>
-      <c r="H68" s="67">
-        <f t="shared" si="10"/>
-        <v>103395</v>
-      </c>
-      <c r="I68" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="179"/>
-      <c r="B69" s="180"/>
-      <c r="C69" s="181"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="60">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="F69" s="49"/>
-      <c r="G69" s="34">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H69" s="67">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
+        <f>E66+F66</f>
+        <v>4856314.9000000004</v>
+      </c>
+      <c r="H66" s="61" t="str">
+        <f>IF(D66=G66, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I66" s="76">
+        <f>D66-G66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="79"/>
+      <c r="B67" s="79"/>
+      <c r="C67" s="79"/>
+      <c r="D67" s="104"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="3"/>
+      <c r="H67" s="61"/>
+    </row>
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="79"/>
+      <c r="B68" s="79"/>
+      <c r="C68" s="79"/>
+      <c r="D68" s="104"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="3"/>
+      <c r="H68" s="61"/>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="79"/>
+      <c r="B69" s="79"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="104"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="3"/>
+      <c r="H69" s="61"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="118" t="s">
-        <v>12</v>
-      </c>
-      <c r="B70" s="122"/>
-      <c r="C70" s="122"/>
-      <c r="D70" s="33">
-        <f>SUM(D49:D69)</f>
-        <v>3606317.41</v>
-      </c>
-      <c r="E70" s="33">
-        <f>SUM(E49:E69)</f>
-        <v>3478442.5491309999</v>
-      </c>
-      <c r="F70" s="33">
-        <f>SUM(F49:F69)</f>
-        <v>127874.86086900001</v>
-      </c>
-      <c r="G70" s="34">
-        <f>E70+F70</f>
-        <v>3606317.41</v>
-      </c>
-      <c r="H70" s="61" t="str">
-        <f>IF(D70=G70, "", "Error")</f>
+      <c r="A70" s="120" t="s">
+        <v>122</v>
+      </c>
+      <c r="B70" s="101"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="37">
+        <v>139000</v>
+      </c>
+      <c r="E70" s="60">
+        <f>D70*91.91%</f>
+        <v>127754.9</v>
+      </c>
+      <c r="F70" s="49">
+        <f>D70*8.09%</f>
+        <v>11245.1</v>
+      </c>
+      <c r="G70" s="66"/>
+      <c r="H70" s="61"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="120" t="s">
+        <v>122</v>
+      </c>
+      <c r="B71" s="140"/>
+      <c r="C71" s="125"/>
+      <c r="D71" s="37">
+        <v>134050</v>
+      </c>
+      <c r="E71" s="60">
+        <f>D71*91.91%</f>
+        <v>123205.355</v>
+      </c>
+      <c r="F71" s="49">
+        <f>D71*8.09%</f>
+        <v>10844.645</v>
+      </c>
+      <c r="G71" s="66"/>
+      <c r="H71" s="61"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="101" t="s">
+        <v>121</v>
+      </c>
+      <c r="B72" s="140"/>
+      <c r="C72" s="125"/>
+      <c r="D72" s="37">
+        <v>112800</v>
+      </c>
+      <c r="E72" s="60">
+        <f>D72</f>
+        <v>112800</v>
+      </c>
+      <c r="F72" s="49">
+        <v>0</v>
+      </c>
+      <c r="G72" s="66"/>
+      <c r="H72" s="61"/>
+    </row>
+    <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="118" t="s">
+        <v>16</v>
+      </c>
+      <c r="B73" s="118"/>
+      <c r="C73" s="118"/>
+      <c r="D73" s="33">
+        <f>SUM(D70:D72)</f>
+        <v>385850</v>
+      </c>
+      <c r="E73" s="33">
+        <f>SUM(E70:E72)</f>
+        <v>363760.255</v>
+      </c>
+      <c r="F73" s="33">
+        <f>SUM(F70:F72)</f>
+        <v>22089.745000000003</v>
+      </c>
+      <c r="G73" s="34">
+        <f>E73+F73</f>
+        <v>385850</v>
+      </c>
+      <c r="H73" s="61" t="str">
+        <f>IF(D73=G73, "", "Error")</f>
         <v/>
       </c>
-      <c r="I70" s="76">
-        <f>D70-G70</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="79"/>
-      <c r="B71" s="79"/>
-      <c r="C71" s="79"/>
-      <c r="D71" s="104"/>
-      <c r="E71" s="39"/>
-      <c r="F71" s="3"/>
-      <c r="H71" s="61"/>
-    </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="79"/>
-      <c r="B72" s="79"/>
-      <c r="C72" s="79"/>
-      <c r="D72" s="104"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="3"/>
-      <c r="H72" s="61"/>
-    </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="79"/>
-      <c r="B73" s="79"/>
-      <c r="C73" s="79"/>
-      <c r="D73" s="104"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="3"/>
-      <c r="H73" s="61"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="120" t="s">
-        <v>143</v>
-      </c>
-      <c r="B74" s="101"/>
+      <c r="J73" s="34"/>
+    </row>
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="79"/>
+      <c r="B74" s="79"/>
       <c r="C74" s="79"/>
-      <c r="D74" s="37">
-        <v>252200</v>
-      </c>
-      <c r="E74" s="60">
-        <f>D74*91.91%</f>
-        <v>231797.02</v>
-      </c>
-      <c r="F74" s="49">
-        <f>D74*8.09%</f>
-        <v>20402.98</v>
-      </c>
-      <c r="G74" s="66"/>
+      <c r="D74" s="104"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="3"/>
       <c r="H74" s="61"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="120" t="s">
-        <v>143</v>
-      </c>
-      <c r="B75" s="140"/>
-      <c r="C75" s="125"/>
-      <c r="D75" s="37">
-        <v>155650</v>
-      </c>
-      <c r="E75" s="60">
-        <f>D75*91.91%</f>
-        <v>143057.91499999998</v>
-      </c>
-      <c r="F75" s="49">
-        <f>D75*8.09%</f>
-        <v>12592.084999999999</v>
-      </c>
-      <c r="G75" s="66"/>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="79"/>
+      <c r="B75" s="79"/>
+      <c r="C75" s="79"/>
+      <c r="D75" s="104"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="3"/>
       <c r="H75" s="61"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="101" t="s">
-        <v>142</v>
-      </c>
-      <c r="B76" s="140"/>
-      <c r="C76" s="125"/>
-      <c r="D76" s="37">
-        <v>112800</v>
-      </c>
-      <c r="E76" s="60">
-        <f>D76</f>
-        <v>112800</v>
-      </c>
-      <c r="F76" s="49">
-        <v>0</v>
-      </c>
-      <c r="G76" s="66"/>
+      <c r="A76" s="119" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" s="79"/>
+      <c r="C76" s="79"/>
+      <c r="D76" s="104"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="3"/>
       <c r="H76" s="61"/>
     </row>
-    <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="118" t="s">
-        <v>16</v>
-      </c>
-      <c r="B77" s="118"/>
-      <c r="C77" s="118"/>
-      <c r="D77" s="33">
-        <f>SUM(D74:D76)</f>
-        <v>520650</v>
-      </c>
-      <c r="E77" s="33">
-        <f>SUM(E74:E76)</f>
-        <v>487654.93499999994</v>
-      </c>
-      <c r="F77" s="33">
-        <f>SUM(F74:F76)</f>
-        <v>32995.065000000002</v>
-      </c>
-      <c r="G77" s="34">
-        <f>E77+F77</f>
-        <v>520649.99999999994</v>
-      </c>
-      <c r="H77" s="61" t="str">
-        <f>IF(D77=G77, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J77" s="34"/>
-    </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="79"/>
+    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="119" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" s="79" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" s="79"/>
+      <c r="D77" s="37">
+        <v>285700</v>
+      </c>
+      <c r="E77" s="60">
+        <f>D77*91.91%</f>
+        <v>262586.87</v>
+      </c>
+      <c r="F77" s="49">
+        <f>D77*8.09%</f>
+        <v>23113.13</v>
+      </c>
+      <c r="G77" t="s">
+        <v>112</v>
+      </c>
+      <c r="H77" s="61"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="119" t="s">
+        <v>80</v>
+      </c>
       <c r="B78" s="79"/>
       <c r="C78" s="79"/>
-      <c r="D78" s="104"/>
-      <c r="E78" s="39"/>
-      <c r="F78" s="3"/>
+      <c r="D78" s="37">
+        <v>45000</v>
+      </c>
+      <c r="E78" s="60">
+        <f>D78*91.91%</f>
+        <v>41359.499999999993</v>
+      </c>
+      <c r="F78" s="49">
+        <f>D78*8.09%</f>
+        <v>3640.5</v>
+      </c>
       <c r="H78" s="61"/>
-    </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="79"/>
+      <c r="J78" s="37"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="119"/>
       <c r="B79" s="79"/>
       <c r="C79" s="79"/>
       <c r="D79" s="104"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="3"/>
+      <c r="E79" s="60">
+        <f>D79*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="49">
+        <f>D79*8.09%</f>
+        <v>0</v>
+      </c>
       <c r="H79" s="61"/>
+      <c r="J79" s="34"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="119" t="s">
-        <v>13</v>
-      </c>
-      <c r="B80" s="79"/>
-      <c r="C80" s="79"/>
-      <c r="D80" s="104"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="3"/>
-      <c r="H80" s="61"/>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="118"/>
+      <c r="B80" s="118"/>
+      <c r="C80" s="118"/>
+      <c r="D80" s="33">
+        <f>SUM(D77:D79)</f>
+        <v>330700</v>
+      </c>
+      <c r="E80" s="33">
+        <f>SUM(E77:E79)</f>
+        <v>303946.37</v>
+      </c>
+      <c r="F80" s="33">
+        <f>SUM(F77:F79)</f>
+        <v>26753.63</v>
+      </c>
+      <c r="G80" s="34">
+        <f>E80+F80</f>
+        <v>330700</v>
+      </c>
+      <c r="H80" s="61" t="str">
+        <f>IF(D80=G80, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J80" s="34"/>
+    </row>
+    <row r="81" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="119" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="79" t="s">
-        <v>127</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B81" s="79"/>
       <c r="C81" s="79"/>
-      <c r="D81" s="37">
-        <v>285700</v>
-      </c>
-      <c r="E81" s="60">
-        <f>D81*91.91%</f>
-        <v>262586.87</v>
-      </c>
-      <c r="F81" s="49">
-        <f>D81*8.09%</f>
-        <v>23113.13</v>
-      </c>
-      <c r="G81" t="s">
-        <v>112</v>
-      </c>
+      <c r="D81" s="37"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="3"/>
       <c r="H81" s="61"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="119" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B82" s="79"/>
       <c r="C82" s="79"/>
       <c r="D82" s="37">
-        <v>45000</v>
+        <v>180218.02</v>
       </c>
       <c r="E82" s="60">
         <f>D82*91.91%</f>
-        <v>41359.499999999993</v>
+        <v>165638.38218199997</v>
       </c>
       <c r="F82" s="49">
         <f>D82*8.09%</f>
-        <v>3640.5</v>
+        <v>14579.637817999999</v>
       </c>
       <c r="H82" s="61"/>
-      <c r="J82" s="37"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="119"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="119" t="s">
+        <v>75</v>
+      </c>
       <c r="B83" s="79"/>
-      <c r="C83" s="79"/>
-      <c r="D83" s="104"/>
+      <c r="C83" s="130"/>
+      <c r="D83" s="37">
+        <v>69000</v>
+      </c>
       <c r="E83" s="60">
         <f>D83*91.91%</f>
-        <v>0</v>
+        <v>63417.899999999994</v>
       </c>
       <c r="F83" s="49">
         <f>D83*8.09%</f>
-        <v>0</v>
+        <v>5582.1</v>
       </c>
       <c r="H83" s="61"/>
-      <c r="J83" s="34"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="118"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="118" t="s">
+        <v>15</v>
+      </c>
       <c r="B84" s="118"/>
       <c r="C84" s="118"/>
-      <c r="D84" s="33">
-        <f>SUM(D81:D83)</f>
-        <v>330700</v>
-      </c>
-      <c r="E84" s="33">
-        <f>SUM(E81:E83)</f>
-        <v>303946.37</v>
-      </c>
-      <c r="F84" s="33">
-        <f>SUM(F81:F83)</f>
-        <v>26753.63</v>
+      <c r="D84" s="64">
+        <f>SUM(D82:D83)</f>
+        <v>249218.02</v>
+      </c>
+      <c r="E84" s="58">
+        <f t="shared" ref="E84:F84" si="22">SUM(E82:E83)</f>
+        <v>229056.28218199997</v>
+      </c>
+      <c r="F84" s="58">
+        <f t="shared" si="22"/>
+        <v>20161.737818000001</v>
       </c>
       <c r="G84" s="34">
         <f>E84+F84</f>
-        <v>330700</v>
+        <v>249218.01999999996</v>
       </c>
       <c r="H84" s="61" t="str">
         <f>IF(D84=G84, "", "Error")</f>
         <v/>
       </c>
-      <c r="J84" s="34"/>
-    </row>
-    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="119" t="s">
-        <v>73</v>
-      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="79"/>
       <c r="B85" s="79"/>
       <c r="C85" s="79"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="40"/>
+      <c r="D85" s="79"/>
+      <c r="E85" s="6"/>
       <c r="F85" s="3"/>
       <c r="H85" s="61"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="119" t="s">
-        <v>74</v>
-      </c>
-      <c r="B86" s="79"/>
-      <c r="C86" s="79"/>
-      <c r="D86" s="37">
-        <f>124723.15-7000</f>
-        <v>117723.15</v>
-      </c>
-      <c r="E86" s="60">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="131" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86" s="131"/>
+      <c r="C86" s="144"/>
+      <c r="D86" s="145"/>
+      <c r="E86" s="143">
         <f>D86*91.91%</f>
-        <v>108199.34716499998</v>
-      </c>
-      <c r="F86" s="49">
+        <v>0</v>
+      </c>
+      <c r="F86" s="51">
         <f>D86*8.09%</f>
-        <v>9523.8028349999986</v>
-      </c>
-      <c r="H86" s="61"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="119" t="s">
-        <v>75</v>
-      </c>
-      <c r="B87" s="79"/>
-      <c r="C87" s="130"/>
-      <c r="D87" s="37">
-        <v>69000</v>
-      </c>
-      <c r="E87" s="60">
-        <f>D87*91.91%</f>
-        <v>63417.899999999994</v>
-      </c>
-      <c r="F87" s="49">
-        <f>D87*8.09%</f>
-        <v>5582.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G86" s="34">
+        <f>E86+F86</f>
+        <v>0</v>
+      </c>
+      <c r="H86" s="61" t="str">
+        <f>IF(D86=G86, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="132"/>
+      <c r="B87" s="78"/>
+      <c r="C87" s="78"/>
+      <c r="D87" s="146"/>
+      <c r="E87" s="147"/>
+      <c r="F87" s="147"/>
+      <c r="G87" s="63"/>
       <c r="H87" s="61"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" s="118"/>
-      <c r="C88" s="118"/>
-      <c r="D88" s="64">
-        <f>SUM(D86:D87)</f>
-        <v>186723.15</v>
-      </c>
-      <c r="E88" s="58">
-        <f t="shared" ref="E88:F88" si="24">SUM(E86:E87)</f>
-        <v>171617.24716499998</v>
-      </c>
-      <c r="F88" s="58">
-        <f t="shared" si="24"/>
-        <v>15105.902834999999</v>
+    <row r="88" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="133" t="s">
+        <v>76</v>
+      </c>
+      <c r="B88" s="134"/>
+      <c r="C88" s="135"/>
+      <c r="D88" s="80">
+        <f>SUM(D86+D84+D80+D73+D66+D47+D32+D27+D42)</f>
+        <v>8819682.2200000007</v>
+      </c>
+      <c r="E88" s="59">
+        <f>SUM(E86+E84+E80+E73+E66+E47+E32+E27+E42)</f>
+        <v>8330246.7564919991</v>
+      </c>
+      <c r="F88" s="148">
+        <f>SUM(F27+F42+F47+F66+F73+F80+F84+F86)</f>
+        <v>489435.46350800002</v>
       </c>
       <c r="G88" s="34">
         <f>E88+F88</f>
-        <v>186723.14999999997</v>
+        <v>8819682.2199999988</v>
       </c>
       <c r="H88" s="61" t="str">
         <f>IF(D88=G88, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="79"/>
-      <c r="B89" s="79"/>
-      <c r="C89" s="79"/>
-      <c r="D89" s="79"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="3"/>
-      <c r="H89" s="61"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="131" t="s">
-        <v>102</v>
-      </c>
-      <c r="B90" s="131"/>
-      <c r="C90" s="144"/>
-      <c r="D90" s="145"/>
-      <c r="E90" s="143">
-        <f>D90*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="51">
-        <f>D90*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G90" s="34">
-        <f>E90+F90</f>
-        <v>0</v>
-      </c>
-      <c r="H90" s="61" t="str">
-        <f>IF(D90=G90, "", "Error")</f>
+      <c r="I88" s="76">
+        <f>D88-G88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="78"/>
+      <c r="B89" s="78"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="78"/>
+      <c r="E89" s="34"/>
+    </row>
+    <row r="90" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="136" t="s">
+        <v>108</v>
+      </c>
+      <c r="B90" s="137"/>
+      <c r="C90" s="137"/>
+      <c r="D90" s="78"/>
+      <c r="E90" s="34"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
+      <c r="C91" s="54"/>
+      <c r="D91" s="78"/>
+      <c r="E91" s="34"/>
+    </row>
+    <row r="92" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="C92" s="54"/>
+      <c r="D92" s="78"/>
+      <c r="E92" s="34"/>
+    </row>
+    <row r="93" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B93" s="57"/>
+      <c r="C93" s="55">
+        <f>SUM(C91:C92)</f>
+        <v>0</v>
+      </c>
+      <c r="E93" s="34"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E94" s="34"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E95" s="52"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="176" t="s">
+        <v>85</v>
+      </c>
+      <c r="B96" s="177"/>
+      <c r="C96" s="177"/>
+      <c r="D96" s="177"/>
+      <c r="E96" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" s="74" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A97" s="173" t="s">
+        <v>135</v>
+      </c>
+      <c r="B97" s="174"/>
+      <c r="C97" s="175"/>
+      <c r="D97" s="37">
+        <v>4000000</v>
+      </c>
+      <c r="E97" s="60">
+        <f t="shared" ref="E97:E100" si="23">D97*91.91%</f>
+        <v>3676399.9999999995</v>
+      </c>
+      <c r="F97" s="49">
+        <f t="shared" ref="F97:F100" si="24">D97*8.09%</f>
+        <v>323600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="178" t="s">
+        <v>136</v>
+      </c>
+      <c r="B98" s="179"/>
+      <c r="C98" s="180"/>
+      <c r="D98" s="37">
+        <v>891000</v>
+      </c>
+      <c r="E98" s="60">
+        <f t="shared" si="23"/>
+        <v>818918.1</v>
+      </c>
+      <c r="F98" s="49">
+        <f t="shared" si="24"/>
+        <v>72081.899999999994</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="212" t="s">
+        <v>138</v>
+      </c>
+      <c r="B99" s="155"/>
+      <c r="C99" s="156"/>
+      <c r="D99" s="37">
+        <v>880000</v>
+      </c>
+      <c r="E99" s="60">
+        <f t="shared" si="23"/>
+        <v>808807.99999999988</v>
+      </c>
+      <c r="F99" s="49">
+        <f t="shared" si="24"/>
+        <v>71192</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="178" t="s">
+        <v>137</v>
+      </c>
+      <c r="B100" s="179"/>
+      <c r="C100" s="180"/>
+      <c r="D100" s="37">
+        <v>713614</v>
+      </c>
+      <c r="E100" s="60">
+        <f t="shared" si="23"/>
+        <v>655882.6274</v>
+      </c>
+      <c r="F100" s="49">
+        <f t="shared" si="24"/>
+        <v>57731.372600000002</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="170" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" s="171"/>
+      <c r="C101" s="172"/>
+      <c r="D101" s="72">
+        <f>SUM(D97:D100)</f>
+        <v>6484614</v>
+      </c>
+      <c r="E101" s="72">
+        <f>SUM(E97:E100)</f>
+        <v>5960008.7273999993</v>
+      </c>
+      <c r="F101" s="72">
+        <f>SUM(F97:F100)</f>
+        <v>524605.27260000003</v>
+      </c>
+      <c r="H101" s="34">
+        <f>E101+F101</f>
+        <v>6484613.9999999991</v>
+      </c>
+      <c r="I101" s="61" t="str">
+        <f>IF(D101=H101, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="132"/>
-      <c r="B91" s="78"/>
-      <c r="C91" s="78"/>
-      <c r="D91" s="146"/>
-      <c r="E91" s="147"/>
-      <c r="F91" s="147"/>
-      <c r="G91" s="63"/>
-      <c r="H91" s="61"/>
-    </row>
-    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="133" t="s">
-        <v>76</v>
-      </c>
-      <c r="B92" s="134"/>
-      <c r="C92" s="135"/>
-      <c r="D92" s="80">
-        <f>SUM(D90+D88+D84+D77+D70+D47+D32+D27+D42)</f>
-        <v>6858637.5199999996</v>
-      </c>
-      <c r="E92" s="59">
-        <f>SUM(E90+E88+E84+E77+E70+E47+E32+E27+E42)</f>
-        <v>6476775.4822319997</v>
-      </c>
-      <c r="F92" s="148">
-        <f>SUM(F27+F42+F47+F70+F77+F84+F88+F90)</f>
-        <v>381862.03776800004</v>
-      </c>
-      <c r="G92" s="34">
-        <f>E92+F92</f>
-        <v>6858637.5199999996</v>
-      </c>
-      <c r="H92" s="61" t="str">
-        <f>IF(D92=G92, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I92" s="76">
-        <f>D92-G92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="78"/>
-      <c r="B93" s="78"/>
-      <c r="C93" s="78"/>
-      <c r="D93" s="78"/>
-      <c r="E93" s="34"/>
-    </row>
-    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="136" t="s">
-        <v>108</v>
-      </c>
-      <c r="B94" s="137"/>
-      <c r="C94" s="137"/>
-      <c r="D94" s="78"/>
-      <c r="E94" s="34"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="C95" s="54"/>
-      <c r="D95" s="78"/>
-      <c r="E95" s="34"/>
-    </row>
-    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1"/>
-      <c r="C96" s="54"/>
-      <c r="D96" s="78"/>
-      <c r="E96" s="34"/>
-    </row>
-    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="56" t="s">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D102" s="34"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="213" t="s">
+        <v>139</v>
+      </c>
+      <c r="B103" s="213"/>
+      <c r="C103" s="213"/>
+      <c r="D103" s="213"/>
+      <c r="E103" s="213"/>
+      <c r="F103" s="213"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="213"/>
+      <c r="B104" s="213"/>
+      <c r="C104" s="213"/>
+      <c r="D104" s="213"/>
+      <c r="E104" s="213"/>
+      <c r="F104" s="213"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="213"/>
+      <c r="B105" s="213"/>
+      <c r="C105" s="213"/>
+      <c r="D105" s="213"/>
+      <c r="E105" s="213"/>
+      <c r="F105" s="213"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="213"/>
+      <c r="B106" s="213"/>
+      <c r="C106" s="213"/>
+      <c r="D106" s="213"/>
+      <c r="E106" s="213"/>
+      <c r="F106" s="213"/>
+    </row>
+    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E107" s="34"/>
+    </row>
+    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B108" s="29">
+        <f>D88</f>
+        <v>8819682.2200000007</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B109" s="31">
+        <f>D88-D86</f>
+        <v>8819682.2200000007</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D110" s="160"/>
+      <c r="E110" s="160"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B111" s="10"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="160"/>
+      <c r="E111" s="160"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B112" s="5">
+        <v>14089108.26</v>
+      </c>
+      <c r="C112" s="13"/>
+      <c r="D112" s="160"/>
+      <c r="E112" s="160"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B113" s="23">
+        <f>PRORRATEO!G52</f>
+        <v>8666282.7266246639</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D113" s="160"/>
+      <c r="E113" s="160"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B114" s="75">
+        <f>-B109</f>
+        <v>-8819682.2200000007</v>
+      </c>
+      <c r="C114" s="11"/>
+      <c r="D114" s="160"/>
+      <c r="E114" s="160"/>
+      <c r="G114" s="37"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B115" s="75">
+        <f>-D101</f>
+        <v>-6484614</v>
+      </c>
+      <c r="C115" s="11"/>
+      <c r="D115" s="160"/>
+      <c r="E115" s="160"/>
+      <c r="G115" s="43"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B116" s="75">
+        <f>-B122</f>
+        <v>0</v>
+      </c>
+      <c r="C116" s="15"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B117" s="24">
+        <f>-C93</f>
+        <v>0</v>
+      </c>
+      <c r="C117" s="15"/>
+      <c r="E117" s="34"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B118" s="16">
+        <f>SUM(B112:B117)</f>
+        <v>7451094.7666246649</v>
+      </c>
+      <c r="C118" s="62">
+        <f>7273784-B125-B118</f>
+        <v>-94616.226624664851</v>
+      </c>
+      <c r="D118" s="34"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="15"/>
+      <c r="C119" s="11"/>
+      <c r="D119" s="18"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C120" s="11"/>
+      <c r="D120" s="34"/>
+      <c r="E120" s="76"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B121" s="86">
+        <f>-82694.54</f>
+        <v>-82694.539999999994</v>
+      </c>
+      <c r="C121" s="17"/>
+      <c r="D121" s="76"/>
+      <c r="E121" s="76"/>
+      <c r="F121" s="76"/>
+    </row>
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" s="24">
+        <v>0</v>
+      </c>
+      <c r="C122" s="17"/>
+      <c r="D122" s="76"/>
+      <c r="E122" s="81"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="12"/>
+      <c r="B123" s="75"/>
+      <c r="C123" s="17"/>
+      <c r="E123" s="34"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="12"/>
+      <c r="B124" s="75"/>
+      <c r="C124" s="17"/>
+      <c r="D124" s="138"/>
+      <c r="E124" s="34"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B97" s="57"/>
-      <c r="C97" s="55">
-        <f>SUM(C95:C96)</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="34"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E98" s="34"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E99" s="52"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="174" t="s">
-        <v>85</v>
-      </c>
-      <c r="B100" s="175"/>
-      <c r="C100" s="175"/>
-      <c r="D100" s="175"/>
-      <c r="E100" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F100" s="74" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A101" s="171"/>
-      <c r="B101" s="172"/>
-      <c r="C101" s="173"/>
-      <c r="D101" s="37"/>
-      <c r="E101" s="60">
-        <f t="shared" ref="E101:E102" si="25">D101*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F101" s="49">
-        <f t="shared" ref="F101:F102" si="26">D101*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="176"/>
-      <c r="B102" s="177"/>
-      <c r="C102" s="178"/>
-      <c r="D102" s="37"/>
-      <c r="E102" s="60">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="F102" s="49">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="168" t="s">
-        <v>25</v>
-      </c>
-      <c r="B103" s="169"/>
-      <c r="C103" s="170"/>
-      <c r="D103" s="72">
-        <f>SUM(D101:D102)</f>
-        <v>0</v>
-      </c>
-      <c r="E103" s="72">
-        <f>SUM(E101:E102)</f>
-        <v>0</v>
-      </c>
-      <c r="F103" s="72">
-        <f>SUM(F101:F102)</f>
-        <v>0</v>
-      </c>
-      <c r="H103" s="34">
-        <f>E103+F103</f>
-        <v>0</v>
-      </c>
-      <c r="I103" s="61" t="str">
-        <f>IF(D103=H103, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E105" s="34"/>
-    </row>
-    <row r="106" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B106" s="29">
-        <f>D92</f>
-        <v>6858637.5199999996</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="B107" s="31">
-        <f>D92-D90</f>
-        <v>6858637.5199999996</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D108" s="158"/>
-      <c r="E108" s="158"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B109" s="10"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="158"/>
-      <c r="E109" s="158"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B110" s="5">
-        <v>12981485.379368611</v>
-      </c>
-      <c r="C110" s="13"/>
-      <c r="D110" s="158"/>
-      <c r="E110" s="158"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B111" s="23">
-        <f>PRORRATEO!G52</f>
-        <v>7986260.3999579996</v>
-      </c>
-      <c r="C111" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D111" s="158"/>
-      <c r="E111" s="158"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B112" s="75">
-        <f>-B107</f>
-        <v>-6858637.5199999996</v>
-      </c>
-      <c r="C112" s="11"/>
-      <c r="D112" s="158"/>
-      <c r="E112" s="158"/>
-      <c r="G112" s="37"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B113" s="75">
-        <f>-D103</f>
-        <v>0</v>
-      </c>
-      <c r="C113" s="11"/>
-      <c r="D113" s="158"/>
-      <c r="E113" s="158"/>
-      <c r="G113" s="43"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A114" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B114" s="75">
-        <f>-B120</f>
-        <v>-20000</v>
-      </c>
-      <c r="C114" s="15"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A115" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B115" s="24">
-        <f>-C97</f>
-        <v>0</v>
-      </c>
-      <c r="C115" s="15"/>
-      <c r="E115" s="34"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A116" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B116" s="16">
-        <f>SUM(B110:B115)</f>
-        <v>14089108.259326611</v>
-      </c>
-      <c r="C116" s="62"/>
-      <c r="D116" s="34"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A117" s="15"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="18"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C118" s="11"/>
-      <c r="D118" s="34"/>
-      <c r="E118" s="76"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A119" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B119" s="86">
-        <v>-102694.54000000004</v>
-      </c>
-      <c r="C119" s="17"/>
-      <c r="D119" s="76"/>
-      <c r="E119" s="76"/>
-      <c r="F119" s="76"/>
-    </row>
-    <row r="120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B120" s="24">
-        <v>20000</v>
-      </c>
-      <c r="C120" s="17"/>
-      <c r="D120" s="76"/>
-      <c r="E120" s="81"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A121" s="12"/>
-      <c r="B121" s="75"/>
-      <c r="C121" s="17"/>
-      <c r="E121" s="34"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A122" s="12"/>
-      <c r="B122" s="75"/>
-      <c r="C122" s="17"/>
-      <c r="D122" s="138"/>
-      <c r="E122" s="34"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A123" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B123" s="27">
-        <f>SUM(B119:B122)</f>
-        <v>-82694.540000000037</v>
-      </c>
-      <c r="C123" s="17"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C124" s="18"/>
-      <c r="D124" s="76"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B125" s="15"/>
-      <c r="C125" s="11"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N127" s="6"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" s="157"/>
-      <c r="C130" s="157"/>
-      <c r="D130" s="157"/>
-      <c r="E130" s="157"/>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B131" s="157"/>
-      <c r="C131" s="157"/>
-      <c r="D131" s="157"/>
-      <c r="E131" s="157"/>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B132" s="157"/>
-      <c r="C132" s="157"/>
-      <c r="D132" s="157"/>
-      <c r="E132" s="157"/>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B133" s="157"/>
-      <c r="C133" s="157"/>
-      <c r="D133" s="157"/>
-      <c r="E133" s="157"/>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B134" s="157"/>
-      <c r="C134" s="157"/>
-      <c r="D134" s="157"/>
-      <c r="E134" s="157"/>
+      <c r="B125" s="27">
+        <f>SUM(B121:B124)</f>
+        <v>-82694.539999999994</v>
+      </c>
+      <c r="C125" s="17"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C126" s="18"/>
+      <c r="D126" s="76"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B127" s="15"/>
+      <c r="C127" s="11"/>
+    </row>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N129" s="6"/>
+    </row>
+    <row r="132" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B132" s="159"/>
+      <c r="C132" s="159"/>
+      <c r="D132" s="159"/>
+      <c r="E132" s="159"/>
+    </row>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B133" s="159"/>
+      <c r="C133" s="159"/>
+      <c r="D133" s="159"/>
+      <c r="E133" s="159"/>
+    </row>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B134" s="159"/>
+      <c r="C134" s="159"/>
+      <c r="D134" s="159"/>
+      <c r="E134" s="159"/>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B135" s="159"/>
+      <c r="C135" s="159"/>
+      <c r="D135" s="159"/>
+      <c r="E135" s="159"/>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B136" s="159"/>
+      <c r="C136" s="159"/>
+      <c r="D136" s="159"/>
+      <c r="E136" s="159"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A60:C60"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B130:E134"/>
-    <mergeCell ref="D108:E113"/>
+    <mergeCell ref="B132:E136"/>
+    <mergeCell ref="D110:E115"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A103:C103"/>
     <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A103:F106"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3859,44 +3844,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="198" t="str">
+      <c r="A1" s="199" t="str">
         <f>RESUMEN!C5</f>
-        <v>VTO: 18/06</v>
-      </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="200"/>
+        <v>VTO: 17/07</v>
+      </c>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="201"/>
       <c r="K1" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="189">
-        <f>RESUMEN!D92</f>
-        <v>6858637.5199999996</v>
-      </c>
-      <c r="M1" s="190"/>
+      <c r="L1" s="188">
+        <f>RESUMEN!D88</f>
+        <v>8819682.2200000007</v>
+      </c>
+      <c r="M1" s="189"/>
       <c r="N1" s="91"/>
       <c r="O1" s="50">
         <f>L1*8.09%</f>
-        <v>554863.77536799992</v>
+        <v>713512.2915980001</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="201"/>
-      <c r="B2" s="202"/>
-      <c r="C2" s="202"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="202"/>
-      <c r="G2" s="202"/>
-      <c r="H2" s="202"/>
-      <c r="I2" s="202"/>
-      <c r="J2" s="203"/>
+      <c r="A2" s="202"/>
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="203"/>
+      <c r="I2" s="203"/>
+      <c r="J2" s="204"/>
       <c r="K2" s="92" t="s">
         <v>95</v>
       </c>
@@ -3908,114 +3893,114 @@
       <c r="N2" s="94"/>
       <c r="O2" s="50">
         <f>O1-K7-553-50-86-8</f>
-        <v>243743.55540999991</v>
+        <v>402392.0716400001</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="201"/>
-      <c r="B3" s="202"/>
-      <c r="C3" s="202"/>
-      <c r="D3" s="202"/>
-      <c r="E3" s="202"/>
-      <c r="F3" s="202"/>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202"/>
-      <c r="J3" s="203"/>
+      <c r="A3" s="202"/>
+      <c r="B3" s="203"/>
+      <c r="C3" s="203"/>
+      <c r="D3" s="203"/>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="203"/>
+      <c r="I3" s="203"/>
+      <c r="J3" s="204"/>
       <c r="K3" s="92" t="s">
         <v>100</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="95">
-        <f>RESUMEN!D103</f>
-        <v>0</v>
+        <f>RESUMEN!D101</f>
+        <v>6484614</v>
       </c>
       <c r="N3" s="96"/>
       <c r="O3" s="8"/>
     </row>
     <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="204"/>
-      <c r="B4" s="205"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="205"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="205"/>
-      <c r="I4" s="205"/>
-      <c r="J4" s="206"/>
+      <c r="A4" s="205"/>
+      <c r="B4" s="206"/>
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="206"/>
+      <c r="J4" s="207"/>
       <c r="K4" s="97" t="s">
         <v>95</v>
       </c>
       <c r="L4" s="98"/>
       <c r="M4" s="99">
-        <v>0</v>
+        <v>1742307</v>
       </c>
       <c r="N4" s="100"/>
       <c r="O4" s="50">
         <f>M3/3</f>
-        <v>0</v>
+        <v>2161538</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="186" t="s">
+      <c r="A5" s="192" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="207" t="s">
+      <c r="B5" s="208" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="186" t="s">
+      <c r="C5" s="192" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="196" t="s">
+      <c r="D5" s="197" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="186" t="s">
+      <c r="E5" s="192" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="186" t="s">
+      <c r="F5" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="186" t="s">
+      <c r="G5" s="192" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="193" t="s">
+      <c r="H5" s="194" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="196" t="s">
+      <c r="I5" s="197" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="191" t="s">
+      <c r="J5" s="190" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="191" t="s">
+      <c r="K5" s="190" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="191" t="s">
+      <c r="L5" s="190" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="191" t="s">
+      <c r="M5" s="190" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="191" t="s">
+      <c r="N5" s="190" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="187"/>
-      <c r="B6" s="208"/>
-      <c r="C6" s="187"/>
-      <c r="D6" s="209"/>
-      <c r="E6" s="187"/>
-      <c r="F6" s="187"/>
-      <c r="G6" s="187"/>
-      <c r="H6" s="194"/>
-      <c r="I6" s="197"/>
-      <c r="J6" s="195"/>
-      <c r="K6" s="192"/>
-      <c r="L6" s="195"/>
-      <c r="M6" s="192"/>
-      <c r="N6" s="192"/>
+      <c r="A6" s="193"/>
+      <c r="B6" s="209"/>
+      <c r="C6" s="193"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="193"/>
+      <c r="F6" s="193"/>
+      <c r="G6" s="193"/>
+      <c r="H6" s="195"/>
+      <c r="I6" s="198"/>
+      <c r="J6" s="196"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="196"/>
+      <c r="M6" s="191"/>
+      <c r="N6" s="191"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -4032,21 +4017,22 @@
         <v>8.09</v>
       </c>
       <c r="F7" s="19">
-        <v>376162.55995799997</v>
+        <v>310423.219958</v>
       </c>
       <c r="G7" s="154">
         <f>F7</f>
-        <v>376162.55995799997</v>
+        <v>310423.219958</v>
       </c>
       <c r="H7" s="46">
         <f>F7-G7</f>
         <v>0</v>
       </c>
       <c r="I7" s="32">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J7" s="19">
-        <v>0</v>
+        <f>M$4*E7%</f>
+        <v>140952.63630000001</v>
       </c>
       <c r="K7" s="19">
         <v>310423.219958</v>
@@ -4054,11 +4040,11 @@
       <c r="L7" s="25"/>
       <c r="M7" s="2">
         <f>K7+J7+H7+L7</f>
-        <v>310423.219958</v>
+        <v>451375.85625800001</v>
       </c>
       <c r="N7" s="5">
         <f>M7*6% + M7</f>
-        <v>329048.61315548001</v>
+        <v>478458.40763348003</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4076,21 +4062,21 @@
         <v>2.21</v>
       </c>
       <c r="F8" s="19">
-        <v>187672.93683118254</v>
+        <v>167564.47683118255</v>
       </c>
       <c r="G8" s="154">
-        <v>190000</v>
+        <v>180000</v>
       </c>
       <c r="H8" s="46">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-2327.0631688174617</v>
+        <v>-12435.523168817454</v>
       </c>
       <c r="I8" s="32">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J8" s="19">
         <f>M$4*E8%</f>
-        <v>0</v>
+        <v>38504.984699999994</v>
       </c>
       <c r="K8" s="19">
         <f>M$2*E8 /100</f>
@@ -4099,11 +4085,11 @@
       <c r="L8" s="88"/>
       <c r="M8" s="2">
         <f>K8+J8+H8+L8</f>
-        <v>167564.47683118255</v>
+        <v>195961.00153118256</v>
       </c>
       <c r="N8" s="5">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>177618.34544105351</v>
+        <v>207718.66162305351</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -4121,22 +4107,22 @@
         <v>4.21</v>
       </c>
       <c r="F9" s="19">
-        <v>357849.60286759672</v>
+        <v>323639.1428675967</v>
       </c>
       <c r="G9" s="105">
-        <f>403750-G34</f>
-        <v>357850</v>
+        <f>365151-G34</f>
+        <v>323639.03999999998</v>
       </c>
       <c r="H9" s="46">
         <f t="shared" si="0"/>
-        <v>-0.39713240327546373</v>
+        <v>0.10286759672453627</v>
       </c>
       <c r="I9" s="32">
         <v>9</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
-        <v>0</v>
+        <v>73351.1247</v>
       </c>
       <c r="K9" s="19">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
@@ -4145,11 +4131,11 @@
       <c r="L9" s="88"/>
       <c r="M9" s="2">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>323639.1428675967</v>
+        <v>396990.76756759669</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" si="1"/>
-        <v>343057.49143965251</v>
+        <v>420810.21362165251</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -4167,21 +4153,21 @@
         <v>2.84</v>
       </c>
       <c r="F10" s="19">
-        <v>241800</v>
+        <v>242122.16</v>
       </c>
       <c r="G10" s="154">
-        <v>218000</v>
+        <v>218322</v>
       </c>
       <c r="H10" s="46">
         <f t="shared" si="0"/>
-        <v>23800</v>
+        <v>23800.160000000003</v>
       </c>
       <c r="I10" s="32">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J10" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49481.518799999998</v>
       </c>
       <c r="K10" s="19">
         <f t="shared" si="3"/>
@@ -4190,11 +4176,11 @@
       <c r="L10" s="88"/>
       <c r="M10" s="2">
         <f t="shared" si="4"/>
-        <v>242122.16</v>
+        <v>291603.83880000003</v>
       </c>
       <c r="N10" s="5">
         <f t="shared" si="1"/>
-        <v>256649.4896</v>
+        <v>309100.069128</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -4212,22 +4198,22 @@
         <v>3.43</v>
       </c>
       <c r="F11" s="19">
-        <v>291550</v>
+        <v>263677.82</v>
       </c>
       <c r="G11" s="154">
         <f>F11</f>
-        <v>291550</v>
+        <v>263677.82</v>
       </c>
       <c r="H11" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11" s="32">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>59761.130100000009</v>
       </c>
       <c r="K11" s="19">
         <f t="shared" si="3"/>
@@ -4236,11 +4222,11 @@
       <c r="L11" s="88"/>
       <c r="M11" s="2">
         <f t="shared" si="4"/>
-        <v>263677.82</v>
+        <v>323438.95010000002</v>
       </c>
       <c r="N11" s="5">
         <f t="shared" si="1"/>
-        <v>279498.48920000001</v>
+        <v>342845.287106</v>
       </c>
       <c r="P11" s="34"/>
     </row>
@@ -4259,11 +4245,11 @@
         <v>2.84</v>
       </c>
       <c r="F12" s="19">
-        <v>241400</v>
+        <v>218322.16</v>
       </c>
       <c r="G12" s="105">
         <f>F12</f>
-        <v>241400</v>
+        <v>218322.16</v>
       </c>
       <c r="H12" s="46">
         <f>F12-G12</f>
@@ -4274,7 +4260,7 @@
       </c>
       <c r="J12" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49481.518799999998</v>
       </c>
       <c r="K12" s="19">
         <f t="shared" si="3"/>
@@ -4283,11 +4269,11 @@
       <c r="L12" s="88"/>
       <c r="M12" s="2">
         <f t="shared" si="4"/>
-        <v>218322.16</v>
+        <v>267803.67879999999</v>
       </c>
       <c r="N12" s="5">
         <f t="shared" si="1"/>
-        <v>231421.4896</v>
+        <v>283871.89952799998</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -4305,22 +4291,22 @@
         <v>3.43</v>
       </c>
       <c r="F13" s="19">
-        <v>291550.81741924176</v>
+        <v>263677.63741924177</v>
       </c>
       <c r="G13" s="105">
-        <f>341701-G50</f>
-        <v>291551</v>
+        <f>309034-G50</f>
+        <v>263678.33999999997</v>
       </c>
       <c r="H13" s="46">
         <f t="shared" si="0"/>
-        <v>-0.18258075823541731</v>
+        <v>-0.7025807581958361</v>
       </c>
       <c r="I13" s="32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J13" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>59761.130100000009</v>
       </c>
       <c r="K13" s="19">
         <f t="shared" si="3"/>
@@ -4329,11 +4315,11 @@
       <c r="L13" s="88"/>
       <c r="M13" s="2">
         <f t="shared" si="4"/>
-        <v>263677.63741924177</v>
+        <v>323438.24751924182</v>
       </c>
       <c r="N13" s="5">
         <f t="shared" si="1"/>
-        <v>279498.29566439625</v>
+        <v>342844.54237039632</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -4351,21 +4337,21 @@
         <v>2.84</v>
       </c>
       <c r="F14" s="19">
-        <v>555195.10466666659</v>
+        <v>588506.98054666666</v>
       </c>
       <c r="G14" s="154">
         <v>218322</v>
       </c>
       <c r="H14" s="46">
         <f t="shared" si="0"/>
-        <v>336873.10466666659</v>
+        <v>370184.98054666666</v>
       </c>
       <c r="I14" s="32">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J14" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49481.518799999998</v>
       </c>
       <c r="K14" s="19">
         <f t="shared" si="3"/>
@@ -4374,11 +4360,11 @@
       <c r="L14" s="88"/>
       <c r="M14" s="2">
         <f t="shared" si="4"/>
-        <v>555195.26466666663</v>
+        <v>637988.65934666665</v>
       </c>
       <c r="N14" s="5">
         <f t="shared" si="1"/>
-        <v>588506.98054666666</v>
+        <v>676267.97890746663</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -4396,19 +4382,22 @@
         <v>3.43</v>
       </c>
       <c r="F15" s="19">
-        <v>291550.06325632613</v>
-      </c>
-      <c r="G15" s="105"/>
+        <v>555227.8832563262</v>
+      </c>
+      <c r="G15" s="105">
+        <f>636165-G35</f>
+        <v>555228</v>
+      </c>
       <c r="H15" s="46">
         <f t="shared" si="0"/>
-        <v>291550.06325632613</v>
+        <v>-0.11674367380328476</v>
       </c>
       <c r="I15" s="32">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J15" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>59761.130100000009</v>
       </c>
       <c r="K15" s="19">
         <f t="shared" si="3"/>
@@ -4417,11 +4406,11 @@
       <c r="L15" s="88"/>
       <c r="M15" s="2">
         <f t="shared" si="4"/>
-        <v>555227.8832563262</v>
+        <v>323438.83335632621</v>
       </c>
       <c r="N15" s="5">
         <f t="shared" si="1"/>
-        <v>588541.55625170574</v>
+        <v>342845.16335770581</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -4439,22 +4428,22 @@
         <v>2.84</v>
       </c>
       <c r="F16" s="19">
-        <v>241400.07982700004</v>
+        <v>218322.23982700004</v>
       </c>
       <c r="G16" s="105">
-        <f>283050-G49</f>
-        <v>241400</v>
+        <f>255990-G49</f>
+        <v>218321.74</v>
       </c>
       <c r="H16" s="46">
         <f t="shared" si="0"/>
-        <v>7.9827000037766993E-2</v>
+        <v>0.49982700005057268</v>
       </c>
       <c r="I16" s="32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J16" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49481.518799999998</v>
       </c>
       <c r="K16" s="19">
         <f t="shared" si="3"/>
@@ -4463,11 +4452,11 @@
       <c r="L16" s="88"/>
       <c r="M16" s="2">
         <f t="shared" si="4"/>
-        <v>218322.23982700004</v>
+        <v>267804.17862700007</v>
       </c>
       <c r="N16" s="5">
         <f t="shared" si="1"/>
-        <v>231421.57421662004</v>
+        <v>283872.42934462009</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -4485,22 +4474,22 @@
         <v>3.43</v>
       </c>
       <c r="F17" s="19">
-        <v>324891.38578511507</v>
+        <v>282068.20578511507</v>
       </c>
       <c r="G17" s="154">
-        <f>380749-G47-G48+14951</f>
-        <v>306501</v>
+        <f>84739.59-G47-G48+278000</f>
+        <v>286634.33</v>
       </c>
       <c r="H17" s="46">
         <f t="shared" si="0"/>
-        <v>18390.385785115068</v>
+        <v>-4566.1242148849415</v>
       </c>
       <c r="I17" s="32">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J17" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>59761.130100000009</v>
       </c>
       <c r="K17" s="19">
         <f t="shared" si="3"/>
@@ -4509,11 +4498,11 @@
       <c r="L17" s="88"/>
       <c r="M17" s="2">
         <f t="shared" si="4"/>
-        <v>282068.20578511507</v>
+        <v>318872.82588511507</v>
       </c>
       <c r="N17" s="5">
         <f t="shared" si="1"/>
-        <v>298992.29813222197</v>
+        <v>338005.19543822197</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -4531,22 +4520,22 @@
         <v>2.84</v>
       </c>
       <c r="F18" s="19">
-        <v>261399.50379991793</v>
+        <v>218321.66379991794</v>
       </c>
       <c r="G18" s="154">
-        <f>309850-G51</f>
-        <v>261400</v>
+        <f>262164-G51</f>
+        <v>218345.82</v>
       </c>
       <c r="H18" s="46">
         <f t="shared" si="0"/>
-        <v>-0.49620008206693456</v>
+        <v>-24.156200082070427</v>
       </c>
       <c r="I18" s="32">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J18" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49481.518799999998</v>
       </c>
       <c r="K18" s="19">
         <f t="shared" si="3"/>
@@ -4555,11 +4544,11 @@
       <c r="L18" s="88"/>
       <c r="M18" s="2">
         <f t="shared" si="4"/>
-        <v>218321.66379991794</v>
+        <v>267779.52259991795</v>
       </c>
       <c r="N18" s="5">
         <f t="shared" si="1"/>
-        <v>231420.96362791301</v>
+        <v>283846.29395591305</v>
       </c>
       <c r="P18" t="s">
         <v>111</v>
@@ -4580,22 +4569,22 @@
         <v>3.43</v>
       </c>
       <c r="F19" s="19">
-        <v>291549.81964850146</v>
+        <v>291549.63964850147</v>
       </c>
       <c r="G19" s="105">
-        <f>309578-G41</f>
-        <v>263678</v>
+        <f>333062-G41</f>
+        <v>291550.03999999998</v>
       </c>
       <c r="H19" s="46">
         <f t="shared" si="0"/>
-        <v>27871.819648501463</v>
+        <v>-0.4003514985088259</v>
       </c>
       <c r="I19" s="32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J19" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>59761.130100000009</v>
       </c>
       <c r="K19" s="19">
         <f t="shared" si="3"/>
@@ -4604,11 +4593,11 @@
       <c r="L19" s="88"/>
       <c r="M19" s="2">
         <f t="shared" si="4"/>
-        <v>291549.63964850147</v>
+        <v>323438.54974850151</v>
       </c>
       <c r="N19" s="5">
         <f t="shared" si="1"/>
-        <v>309042.61802741158</v>
+        <v>342844.8627334116</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -4626,22 +4615,22 @@
         <v>2.84</v>
       </c>
       <c r="F20" s="19">
-        <v>241399.65585707471</v>
+        <v>218321.81585707472</v>
       </c>
       <c r="G20" s="154">
-        <f>283050-G38</f>
-        <v>241400</v>
+        <f>255990-G38</f>
+        <v>218321.74</v>
       </c>
       <c r="H20" s="46">
         <f t="shared" si="0"/>
-        <v>-0.34414292528526857</v>
+        <v>7.585707472753711E-2</v>
       </c>
       <c r="I20" s="32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J20" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49481.518799999998</v>
       </c>
       <c r="K20" s="19">
         <f t="shared" si="3"/>
@@ -4650,11 +4639,11 @@
       <c r="L20" s="88"/>
       <c r="M20" s="2">
         <f t="shared" si="4"/>
-        <v>218321.81585707472</v>
+        <v>267803.75465707469</v>
       </c>
       <c r="N20" s="5">
         <f t="shared" si="1"/>
-        <v>231421.12480849921</v>
+        <v>283871.97993649915</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4672,22 +4661,22 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="19">
-        <v>291549.9952936371</v>
+        <v>263677.8152936371</v>
       </c>
       <c r="G21" s="154">
-        <f>337450-G45</f>
-        <v>291550</v>
+        <f>305190-G45</f>
+        <v>263678.03999999998</v>
       </c>
       <c r="H21" s="46">
         <f t="shared" si="0"/>
-        <v>-4.7063629026524723E-3</v>
+        <v>-0.2247063628747128</v>
       </c>
       <c r="I21" s="32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J21" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>59761.130100000009</v>
       </c>
       <c r="K21" s="19">
         <f t="shared" si="3"/>
@@ -4696,11 +4685,11 @@
       <c r="L21" s="88"/>
       <c r="M21" s="2">
         <f t="shared" si="4"/>
-        <v>263677.8152936371</v>
+        <v>323438.72539363714</v>
       </c>
       <c r="N21" s="5">
         <f t="shared" si="1"/>
-        <v>279498.48421125533</v>
+        <v>342845.04891725536</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4718,11 +4707,11 @@
         <v>2.84</v>
       </c>
       <c r="F22" s="19">
-        <v>241400</v>
+        <v>218322.16</v>
       </c>
       <c r="G22" s="154">
         <f>F22</f>
-        <v>241400</v>
+        <v>218322.16</v>
       </c>
       <c r="H22" s="46">
         <f t="shared" si="0"/>
@@ -4733,7 +4722,7 @@
       </c>
       <c r="J22" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49481.518799999998</v>
       </c>
       <c r="K22" s="19">
         <f t="shared" si="3"/>
@@ -4742,11 +4731,11 @@
       <c r="L22" s="88"/>
       <c r="M22" s="2">
         <f t="shared" si="4"/>
-        <v>218322.16</v>
+        <v>267803.67879999999</v>
       </c>
       <c r="N22" s="5">
         <f t="shared" si="1"/>
-        <v>231421.4896</v>
+        <v>283871.89952799998</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -4764,22 +4753,22 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="19">
-        <v>290748.66790342226</v>
+        <v>261926.48790342227</v>
       </c>
       <c r="G23" s="105">
-        <f>335000-G46</f>
-        <v>292500</v>
+        <f>340000-G46</f>
+        <v>301563</v>
       </c>
       <c r="H23" s="46">
         <f t="shared" si="0"/>
-        <v>-1751.3320965777384</v>
+        <v>-39636.512096577731</v>
       </c>
       <c r="I23" s="32">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J23" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>59761.130100000009</v>
       </c>
       <c r="K23" s="19">
         <f t="shared" si="3"/>
@@ -4788,11 +4777,11 @@
       <c r="L23" s="88"/>
       <c r="M23" s="2">
         <f t="shared" si="4"/>
-        <v>261926.48790342227</v>
+        <v>283802.43800342228</v>
       </c>
       <c r="N23" s="5">
         <f t="shared" si="1"/>
-        <v>277642.07717762759</v>
+        <v>300830.58428362763</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4810,22 +4799,22 @@
         <v>2.84</v>
       </c>
       <c r="F24" s="19">
-        <v>240835.37342107471</v>
+        <v>210807.53342107471</v>
       </c>
       <c r="G24" s="154">
-        <f>290000-G37</f>
-        <v>248350</v>
+        <f>248476-G37</f>
+        <v>210807.74</v>
       </c>
       <c r="H24" s="46">
         <f t="shared" si="0"/>
-        <v>-7514.6265789252939</v>
+        <v>-0.20657892528106458</v>
       </c>
       <c r="I24" s="77">
         <v>7</v>
       </c>
       <c r="J24" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49481.518799999998</v>
       </c>
       <c r="K24" s="19">
         <f t="shared" si="3"/>
@@ -4834,11 +4823,11 @@
       <c r="L24" s="88"/>
       <c r="M24" s="2">
         <f t="shared" si="4"/>
-        <v>210807.53342107471</v>
+        <v>267803.47222107474</v>
       </c>
       <c r="N24" s="5">
         <f t="shared" si="1"/>
-        <v>223455.9854263392</v>
+        <v>283871.6805543392</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -4856,21 +4845,22 @@
         <v>3.43</v>
       </c>
       <c r="F25" s="19">
-        <v>275750.79666666669</v>
+        <v>247131.77666666667</v>
       </c>
       <c r="G25" s="105">
-        <v>292296.84000000003</v>
+        <f>F25</f>
+        <v>247131.77666666667</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="0"/>
-        <v>-16546.043333333335</v>
+        <v>0</v>
       </c>
       <c r="I25" s="32">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J25" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>59761.130100000009</v>
       </c>
       <c r="K25" s="19">
         <f t="shared" si="3"/>
@@ -4879,11 +4869,11 @@
       <c r="L25" s="89"/>
       <c r="M25" s="2">
         <f t="shared" si="4"/>
-        <v>247131.77666666667</v>
+        <v>323438.95010000002</v>
       </c>
       <c r="N25" s="5">
         <f t="shared" si="1"/>
-        <v>261959.68326666666</v>
+        <v>342845.287106</v>
       </c>
       <c r="P25" s="53"/>
       <c r="Q25" s="53"/>
@@ -4904,22 +4894,22 @@
         <v>6</v>
       </c>
       <c r="F26" s="19">
-        <v>-2243661.3406672962</v>
+        <v>-1647267.3406672962</v>
       </c>
       <c r="G26" s="105">
-        <f>-G30-G31-G36</f>
-        <v>-135150</v>
+        <f>600000+900000-G30-G31-G36</f>
+        <v>1377770.34</v>
       </c>
       <c r="H26" s="47">
         <f t="shared" si="0"/>
-        <v>-2108511.3406672962</v>
-      </c>
-      <c r="I26" s="149" t="s">
-        <v>145</v>
+        <v>-3025037.6806672961</v>
+      </c>
+      <c r="I26" s="149">
+        <v>1</v>
       </c>
       <c r="J26" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>104538.42</v>
       </c>
       <c r="K26" s="19">
         <f t="shared" si="3"/>
@@ -4928,11 +4918,11 @@
       <c r="L26" s="88"/>
       <c r="M26" s="2">
         <f t="shared" si="4"/>
-        <v>-1647267.3406672962</v>
+        <v>-2459255.2606672961</v>
       </c>
       <c r="N26" s="5">
         <f t="shared" si="1"/>
-        <v>-1746103.381107334</v>
+        <v>-2606810.576307334</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -4950,22 +4940,22 @@
         <v>5.89</v>
       </c>
       <c r="F27" s="19">
-        <v>500650.37128526531</v>
+        <v>452038.2312852653</v>
       </c>
       <c r="G27" s="154">
-        <f>600000-G39-G40</f>
-        <v>501400</v>
+        <f>541100-G39-G40</f>
+        <v>451926.16</v>
       </c>
       <c r="H27" s="46">
         <f t="shared" si="0"/>
-        <v>-749.6287147346884</v>
+        <v>112.07128526532324</v>
       </c>
       <c r="I27" s="32">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J27" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>102621.88229999998</v>
       </c>
       <c r="K27" s="19">
         <f t="shared" si="3"/>
@@ -4974,11 +4964,11 @@
       <c r="L27" s="88"/>
       <c r="M27" s="2">
         <f t="shared" si="4"/>
-        <v>452038.2312852653</v>
+        <v>555521.81358526531</v>
       </c>
       <c r="N27" s="5">
         <f t="shared" si="1"/>
-        <v>479160.52516238124</v>
+        <v>588853.12240038125</v>
       </c>
       <c r="R27" s="53"/>
     </row>
@@ -4997,22 +4987,22 @@
         <v>5.89</v>
       </c>
       <c r="F28" s="19">
-        <v>499341.17449320736</v>
+        <v>442229.03449320735</v>
       </c>
       <c r="G28" s="154">
-        <f>600000-G32-G33</f>
-        <v>509900</v>
+        <f>525000-G32-G33</f>
+        <v>443513.56</v>
       </c>
       <c r="H28" s="46">
         <f t="shared" si="0"/>
-        <v>-10558.825506792637</v>
+        <v>-1284.5255067926482</v>
       </c>
       <c r="I28" s="32">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J28" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>102621.88229999998</v>
       </c>
       <c r="K28" s="19">
         <f t="shared" si="3"/>
@@ -5021,11 +5011,11 @@
       <c r="L28" s="88"/>
       <c r="M28" s="2">
         <f t="shared" si="4"/>
-        <v>442229.03449320735</v>
+        <v>554125.21679320722</v>
       </c>
       <c r="N28" s="5">
         <f t="shared" si="1"/>
-        <v>468762.77656279982</v>
+        <v>587372.72980079963</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -5043,22 +5033,22 @@
         <v>5.89</v>
       </c>
       <c r="F29" s="19">
-        <v>1129090.7461941019</v>
+        <v>427578.60619410186</v>
       </c>
       <c r="G29" s="105">
-        <f>1428000-G42-G43-G44</f>
-        <v>1154300</v>
+        <f>551700-G42-G43-G44</f>
+        <v>427932.86</v>
       </c>
       <c r="H29" s="47">
         <f t="shared" si="0"/>
-        <v>-25209.25380589813</v>
+        <v>-354.25380589812994</v>
       </c>
       <c r="I29" s="32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J29" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>102621.88229999998</v>
       </c>
       <c r="K29" s="19">
         <f t="shared" si="3"/>
@@ -5067,11 +5057,11 @@
       <c r="L29" s="88"/>
       <c r="M29" s="2">
         <f t="shared" si="4"/>
-        <v>427578.60619410186</v>
+        <v>555055.4884941018</v>
       </c>
       <c r="N29" s="5">
         <f t="shared" si="1"/>
-        <v>453233.32256574795</v>
+        <v>588358.81780374795</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -5089,11 +5079,11 @@
         <v>0.54</v>
       </c>
       <c r="F30" s="19">
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="G30" s="154">
         <f>F30</f>
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="H30" s="46">
         <f t="shared" si="0"/>
@@ -5102,7 +5092,7 @@
       <c r="I30" s="32"/>
       <c r="J30" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9408.4578000000001</v>
       </c>
       <c r="K30" s="19">
         <f t="shared" si="3"/>
@@ -5111,11 +5101,11 @@
       <c r="L30" s="88"/>
       <c r="M30" s="2">
         <f t="shared" si="4"/>
-        <v>41511.960000000006</v>
+        <v>50920.41780000001</v>
       </c>
       <c r="N30" s="5">
         <f t="shared" si="1"/>
-        <v>44002.67760000001</v>
+        <v>53975.64286800001</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -5133,11 +5123,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F31" s="19">
-        <v>46750</v>
+        <v>42280.7</v>
       </c>
       <c r="G31" s="154">
         <f>F31</f>
-        <v>46750</v>
+        <v>42280.7</v>
       </c>
       <c r="H31" s="46">
         <f t="shared" si="0"/>
@@ -5146,7 +5136,7 @@
       <c r="I31" s="32"/>
       <c r="J31" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9582.6885000000002</v>
       </c>
       <c r="K31" s="19">
         <f t="shared" si="3"/>
@@ -5155,11 +5145,11 @@
       <c r="L31" s="88"/>
       <c r="M31" s="2">
         <f t="shared" si="4"/>
-        <v>42280.7</v>
+        <v>51863.388500000001</v>
       </c>
       <c r="N31" s="5">
         <f t="shared" si="1"/>
-        <v>44817.541999999994</v>
+        <v>54975.191810000004</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -5177,11 +5167,11 @@
         <v>0.45</v>
       </c>
       <c r="F32" s="19">
-        <v>38250</v>
+        <v>34593.300000000003</v>
       </c>
       <c r="G32" s="154">
         <f>F32</f>
-        <v>38250</v>
+        <v>34593.300000000003</v>
       </c>
       <c r="H32" s="46">
         <f t="shared" si="0"/>
@@ -5190,7 +5180,7 @@
       <c r="I32" s="32"/>
       <c r="J32" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7840.3815000000013</v>
       </c>
       <c r="K32" s="19">
         <f t="shared" si="3"/>
@@ -5199,11 +5189,11 @@
       <c r="L32" s="68"/>
       <c r="M32" s="2">
         <f t="shared" si="4"/>
-        <v>34593.300000000003</v>
+        <v>42433.681500000006</v>
       </c>
       <c r="N32" s="5">
         <f t="shared" si="1"/>
-        <v>36668.898000000001</v>
+        <v>44979.702390000006</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -5221,11 +5211,11 @@
         <v>0.61</v>
       </c>
       <c r="F33" s="19">
-        <v>51850</v>
+        <v>46893.14</v>
       </c>
       <c r="G33" s="154">
         <f t="shared" ref="G33" si="5">F33</f>
-        <v>51850</v>
+        <v>46893.14</v>
       </c>
       <c r="H33" s="46">
         <f t="shared" si="0"/>
@@ -5234,7 +5224,7 @@
       <c r="I33" s="32"/>
       <c r="J33" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10628.072699999999</v>
       </c>
       <c r="K33" s="19">
         <f t="shared" si="3"/>
@@ -5243,11 +5233,11 @@
       <c r="L33" s="68"/>
       <c r="M33" s="2">
         <f t="shared" si="4"/>
-        <v>46893.14</v>
+        <v>57521.212699999996</v>
       </c>
       <c r="N33" s="5">
         <f t="shared" si="1"/>
-        <v>49706.7284</v>
+        <v>60972.485461999997</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -5265,11 +5255,11 @@
         <v>0.54</v>
       </c>
       <c r="F34" s="19">
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="G34" s="154">
         <f>F34</f>
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="H34" s="46">
         <f t="shared" si="0"/>
@@ -5278,7 +5268,7 @@
       <c r="I34" s="32"/>
       <c r="J34" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9408.4578000000001</v>
       </c>
       <c r="K34" s="19">
         <f t="shared" si="3"/>
@@ -5287,11 +5277,11 @@
       <c r="L34" s="68"/>
       <c r="M34" s="2">
         <f t="shared" si="4"/>
-        <v>41511.960000000006</v>
+        <v>50920.41780000001</v>
       </c>
       <c r="N34" s="5">
         <f t="shared" si="1"/>
-        <v>44002.67760000001</v>
+        <v>53975.64286800001</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -5308,18 +5298,21 @@
       <c r="E35" s="3">
         <v>0.5</v>
       </c>
-      <c r="F35" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G35" s="105"/>
+      <c r="F35" s="214">
+        <v>80937</v>
+      </c>
+      <c r="G35" s="105">
+        <f>F35</f>
+        <v>80937</v>
+      </c>
       <c r="H35" s="46">
         <f t="shared" si="0"/>
-        <v>42500</v>
+        <v>0</v>
       </c>
       <c r="I35" s="32"/>
       <c r="J35" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8711.5349999999999</v>
       </c>
       <c r="K35" s="19">
         <f t="shared" si="3"/>
@@ -5328,11 +5321,11 @@
       <c r="L35" s="68"/>
       <c r="M35" s="2">
         <f t="shared" si="4"/>
-        <v>80937</v>
+        <v>47148.535000000003</v>
       </c>
       <c r="N35" s="5">
         <f t="shared" si="1"/>
-        <v>85793.22</v>
+        <v>49977.447100000005</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -5350,11 +5343,11 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="19">
-        <v>42500</v>
+        <v>38437</v>
       </c>
       <c r="G36" s="154">
         <f>F36</f>
-        <v>42500</v>
+        <v>38437</v>
       </c>
       <c r="H36" s="46">
         <f t="shared" si="0"/>
@@ -5363,7 +5356,7 @@
       <c r="I36" s="32"/>
       <c r="J36" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8711.5349999999999</v>
       </c>
       <c r="K36" s="19">
         <f t="shared" si="3"/>
@@ -5372,11 +5365,11 @@
       <c r="L36" s="68"/>
       <c r="M36" s="2">
         <f t="shared" si="4"/>
-        <v>38437</v>
+        <v>47148.535000000003</v>
       </c>
       <c r="N36" s="5">
         <f t="shared" si="1"/>
-        <v>40743.22</v>
+        <v>49977.447100000005</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -5394,11 +5387,11 @@
         <v>0.49</v>
       </c>
       <c r="F37" s="19">
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="G37" s="154">
         <f t="shared" ref="G37:G41" si="6">F37</f>
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="H37" s="46">
         <f t="shared" si="0"/>
@@ -5407,7 +5400,7 @@
       <c r="I37" s="32"/>
       <c r="J37" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8537.3042999999998</v>
       </c>
       <c r="K37" s="19">
         <f t="shared" si="3"/>
@@ -5416,11 +5409,11 @@
       <c r="L37" s="68"/>
       <c r="M37" s="2">
         <f t="shared" si="4"/>
-        <v>37668.26</v>
+        <v>46205.564299999998</v>
       </c>
       <c r="N37" s="5">
         <f t="shared" si="1"/>
-        <v>39928.355600000003</v>
+        <v>48977.898157999996</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -5438,11 +5431,11 @@
         <v>0.49</v>
       </c>
       <c r="F38" s="19">
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="G38" s="154">
         <f t="shared" si="6"/>
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="H38" s="46">
         <f t="shared" si="0"/>
@@ -5451,7 +5444,7 @@
       <c r="I38" s="32"/>
       <c r="J38" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8537.3042999999998</v>
       </c>
       <c r="K38" s="19">
         <f t="shared" si="3"/>
@@ -5460,11 +5453,11 @@
       <c r="L38" s="68"/>
       <c r="M38" s="2">
         <f t="shared" si="4"/>
-        <v>37668.26</v>
+        <v>46205.564299999998</v>
       </c>
       <c r="N38" s="5">
         <f t="shared" si="1"/>
-        <v>39928.355600000003</v>
+        <v>48977.898157999996</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -5482,11 +5475,11 @@
         <v>0.59</v>
       </c>
       <c r="F39" s="19">
-        <v>50150</v>
+        <v>45355.66</v>
       </c>
       <c r="G39" s="154">
         <f t="shared" si="6"/>
-        <v>50150</v>
+        <v>45355.66</v>
       </c>
       <c r="H39" s="46">
         <f t="shared" si="0"/>
@@ -5495,7 +5488,7 @@
       <c r="I39" s="32"/>
       <c r="J39" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10279.6113</v>
       </c>
       <c r="K39" s="19">
         <f t="shared" si="3"/>
@@ -5504,11 +5497,11 @@
       <c r="L39" s="68"/>
       <c r="M39" s="2">
         <f t="shared" si="4"/>
-        <v>45355.66</v>
+        <v>55635.271300000008</v>
       </c>
       <c r="N39" s="5">
         <f t="shared" si="1"/>
-        <v>48076.999600000003</v>
+        <v>58973.387578000009</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -5526,11 +5519,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F40" s="19">
-        <v>48450</v>
+        <v>43818.18</v>
       </c>
       <c r="G40" s="154">
         <f t="shared" si="6"/>
-        <v>48450</v>
+        <v>43818.18</v>
       </c>
       <c r="H40" s="46">
         <f t="shared" si="0"/>
@@ -5539,7 +5532,7 @@
       <c r="I40" s="32"/>
       <c r="J40" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9931.1498999999985</v>
       </c>
       <c r="K40" s="19">
         <f t="shared" si="3"/>
@@ -5548,11 +5541,11 @@
       <c r="L40" s="68"/>
       <c r="M40" s="2">
         <f t="shared" si="4"/>
-        <v>43818.18</v>
+        <v>53749.329899999997</v>
       </c>
       <c r="N40" s="5">
         <f t="shared" si="1"/>
-        <v>46447.270799999998</v>
+        <v>56974.289693999999</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -5570,11 +5563,11 @@
         <v>0.54</v>
       </c>
       <c r="F41" s="19">
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="G41" s="154">
         <f t="shared" si="6"/>
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="H41" s="46">
         <f t="shared" si="0"/>
@@ -5583,7 +5576,7 @@
       <c r="I41" s="32"/>
       <c r="J41" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9408.4578000000001</v>
       </c>
       <c r="K41" s="19">
         <f t="shared" si="3"/>
@@ -5592,11 +5585,11 @@
       <c r="L41" s="68"/>
       <c r="M41" s="2">
         <f t="shared" si="4"/>
-        <v>41511.960000000006</v>
+        <v>50920.41780000001</v>
       </c>
       <c r="N41" s="5">
         <f t="shared" si="1"/>
-        <v>44002.67760000001</v>
+        <v>53975.64286800001</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -5614,11 +5607,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="19">
-        <v>93500</v>
+        <v>42280.7</v>
       </c>
       <c r="G42" s="154">
         <f>F42</f>
-        <v>93500</v>
+        <v>42280.7</v>
       </c>
       <c r="H42" s="46">
         <f t="shared" si="0"/>
@@ -5627,7 +5620,7 @@
       <c r="I42" s="32"/>
       <c r="J42" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9582.6885000000002</v>
       </c>
       <c r="K42" s="19">
         <f t="shared" si="3"/>
@@ -5636,11 +5629,11 @@
       <c r="L42" s="68"/>
       <c r="M42" s="2">
         <f t="shared" si="4"/>
-        <v>42280.7</v>
+        <v>51863.388500000001</v>
       </c>
       <c r="N42" s="5">
         <f t="shared" si="1"/>
-        <v>44817.541999999994</v>
+        <v>54975.191810000004</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -5658,11 +5651,11 @@
         <v>0.45</v>
       </c>
       <c r="F43" s="19">
-        <v>76500</v>
+        <v>34593.300000000003</v>
       </c>
       <c r="G43" s="154">
         <f>F43</f>
-        <v>76500</v>
+        <v>34593.300000000003</v>
       </c>
       <c r="H43" s="46">
         <f t="shared" si="0"/>
@@ -5671,7 +5664,7 @@
       <c r="I43" s="32"/>
       <c r="J43" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7840.3815000000013</v>
       </c>
       <c r="K43" s="19">
         <f t="shared" si="3"/>
@@ -5680,15 +5673,15 @@
       <c r="L43" s="68"/>
       <c r="M43" s="2">
         <f t="shared" si="4"/>
-        <v>34593.300000000003</v>
+        <v>42433.681500000006</v>
       </c>
       <c r="N43" s="5">
         <f t="shared" si="1"/>
-        <v>36668.898000000001</v>
+        <v>44979.702390000006</v>
       </c>
       <c r="P43" s="34">
         <f>L1-K52</f>
-        <v>-517275.03995799925</v>
+        <v>1443769.6600420019</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -5706,11 +5699,11 @@
         <v>0.61</v>
       </c>
       <c r="F44" s="19">
-        <v>103700</v>
+        <v>46893.14</v>
       </c>
       <c r="G44" s="154">
         <f>F44</f>
-        <v>103700</v>
+        <v>46893.14</v>
       </c>
       <c r="H44" s="46">
         <f t="shared" si="0"/>
@@ -5719,7 +5712,7 @@
       <c r="I44" s="32"/>
       <c r="J44" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10628.072699999999</v>
       </c>
       <c r="K44" s="19">
         <f t="shared" si="3"/>
@@ -5728,11 +5721,11 @@
       <c r="L44" s="68"/>
       <c r="M44" s="2">
         <f t="shared" si="4"/>
-        <v>46893.14</v>
+        <v>57521.212699999996</v>
       </c>
       <c r="N44" s="5">
         <f t="shared" si="1"/>
-        <v>49706.7284</v>
+        <v>60972.485461999997</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -5750,11 +5743,11 @@
         <v>0.54</v>
       </c>
       <c r="F45" s="19">
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="G45" s="154">
         <f t="shared" ref="G45" si="7">F45</f>
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="H45" s="46">
         <f t="shared" si="0"/>
@@ -5763,7 +5756,7 @@
       <c r="I45" s="32"/>
       <c r="J45" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9408.4578000000001</v>
       </c>
       <c r="K45" s="19">
         <f t="shared" si="3"/>
@@ -5772,11 +5765,11 @@
       <c r="L45" s="68"/>
       <c r="M45" s="2">
         <f t="shared" si="4"/>
-        <v>41511.960000000006</v>
+        <v>50920.41780000001</v>
       </c>
       <c r="N45" s="5">
         <f t="shared" si="1"/>
-        <v>44002.67760000001</v>
+        <v>53975.64286800001</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -5794,11 +5787,11 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="19">
-        <v>42500</v>
+        <v>38437</v>
       </c>
       <c r="G46" s="154">
         <f t="shared" ref="G46:G51" si="8">F46</f>
-        <v>42500</v>
+        <v>38437</v>
       </c>
       <c r="H46" s="46">
         <f t="shared" si="0"/>
@@ -5807,7 +5800,7 @@
       <c r="I46" s="32"/>
       <c r="J46" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8711.5349999999999</v>
       </c>
       <c r="K46" s="19">
         <f t="shared" si="3"/>
@@ -5816,11 +5809,11 @@
       <c r="L46" s="68"/>
       <c r="M46" s="2">
         <f t="shared" si="4"/>
-        <v>38437</v>
+        <v>47148.535000000003</v>
       </c>
       <c r="N46" s="5">
         <f t="shared" si="1"/>
-        <v>40743.22</v>
+        <v>49977.447100000005</v>
       </c>
       <c r="Q46" t="s">
         <v>101</v>
@@ -5841,11 +5834,11 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="19">
-        <v>45050</v>
+        <v>38437</v>
       </c>
       <c r="G47" s="154">
         <f t="shared" si="8"/>
-        <v>45050</v>
+        <v>38437</v>
       </c>
       <c r="H47" s="46">
         <f t="shared" si="0"/>
@@ -5854,7 +5847,7 @@
       <c r="I47" s="32"/>
       <c r="J47" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8711.5349999999999</v>
       </c>
       <c r="K47" s="19">
         <f t="shared" si="3"/>
@@ -5863,16 +5856,16 @@
       <c r="L47" s="68"/>
       <c r="M47" s="2">
         <f t="shared" si="4"/>
-        <v>38437</v>
+        <v>47148.535000000003</v>
       </c>
       <c r="N47" s="5">
         <f t="shared" si="1"/>
-        <v>40743.22</v>
+        <v>49977.447100000005</v>
       </c>
       <c r="O47" s="53"/>
       <c r="Q47" s="50">
         <f>M3-J52</f>
-        <v>0</v>
+        <v>4883259.6363000013</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -5890,11 +5883,11 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="19">
-        <v>44149</v>
+        <v>37668.26</v>
       </c>
       <c r="G48" s="154">
         <f t="shared" si="8"/>
-        <v>44149</v>
+        <v>37668.26</v>
       </c>
       <c r="H48" s="46">
         <f t="shared" si="0"/>
@@ -5903,7 +5896,7 @@
       <c r="I48" s="32"/>
       <c r="J48" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8537.3042999999998</v>
       </c>
       <c r="K48" s="19">
         <f t="shared" si="3"/>
@@ -5912,11 +5905,11 @@
       <c r="L48" s="68"/>
       <c r="M48" s="2">
         <f t="shared" si="4"/>
-        <v>37668.26</v>
+        <v>46205.564299999998</v>
       </c>
       <c r="N48" s="5">
         <f t="shared" si="1"/>
-        <v>39928.355600000003</v>
+        <v>48977.898157999996</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -5935,11 +5928,11 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="19">
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="G49" s="154">
         <f t="shared" si="8"/>
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="H49" s="46">
         <f t="shared" si="0"/>
@@ -5948,7 +5941,7 @@
       <c r="I49" s="32"/>
       <c r="J49" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8537.3042999999998</v>
       </c>
       <c r="K49" s="19">
         <f t="shared" si="3"/>
@@ -5957,11 +5950,11 @@
       <c r="L49" s="68"/>
       <c r="M49" s="2">
         <f t="shared" si="4"/>
-        <v>37668.26</v>
+        <v>46205.564299999998</v>
       </c>
       <c r="N49" s="5">
         <f t="shared" si="1"/>
-        <v>39928.355600000003</v>
+        <v>48977.898157999996</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -5979,11 +5972,11 @@
         <v>0.59</v>
       </c>
       <c r="F50" s="19">
-        <v>50150</v>
+        <v>45355.66</v>
       </c>
       <c r="G50" s="105">
         <f t="shared" si="8"/>
-        <v>50150</v>
+        <v>45355.66</v>
       </c>
       <c r="H50" s="46">
         <f t="shared" si="0"/>
@@ -5992,7 +5985,7 @@
       <c r="I50" s="32"/>
       <c r="J50" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10279.6113</v>
       </c>
       <c r="K50" s="19">
         <f t="shared" si="3"/>
@@ -6001,11 +5994,11 @@
       <c r="L50" s="68"/>
       <c r="M50" s="2">
         <f t="shared" si="4"/>
-        <v>45355.66</v>
+        <v>55635.271300000008</v>
       </c>
       <c r="N50" s="5">
         <f t="shared" si="1"/>
-        <v>48076.999600000003</v>
+        <v>58973.387578000009</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -6023,11 +6016,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F51" s="19">
-        <v>48450</v>
+        <v>43818.18</v>
       </c>
       <c r="G51" s="154">
         <f t="shared" si="8"/>
-        <v>48450</v>
+        <v>43818.18</v>
       </c>
       <c r="H51" s="46">
         <f t="shared" si="0"/>
@@ -6036,7 +6029,7 @@
       <c r="I51" s="32"/>
       <c r="J51" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9931.1498999999985</v>
       </c>
       <c r="K51" s="19">
         <f t="shared" si="3"/>
@@ -6045,11 +6038,11 @@
       <c r="L51" s="68"/>
       <c r="M51" s="2">
         <f t="shared" si="4"/>
-        <v>43818.18</v>
+        <v>53749.329899999997</v>
       </c>
       <c r="N51" s="5">
         <f t="shared" si="1"/>
-        <v>46447.270799999998</v>
+        <v>56974.289693999999</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6063,17 +6056,17 @@
       </c>
       <c r="F52" s="85">
         <f>SUM(F7:F51)</f>
-        <v>6554076.3145067021</v>
+        <v>5977040.1903867004</v>
       </c>
       <c r="G52" s="85">
         <f>SUM(G7:G51)</f>
-        <v>7986260.3999579996</v>
+        <v>8666282.7266246639</v>
       </c>
       <c r="H52" s="20"/>
       <c r="I52" s="20"/>
       <c r="J52" s="45">
         <f>SUM(J8:J51)</f>
-        <v>0</v>
+        <v>1601354.3636999985</v>
       </c>
       <c r="K52" s="21">
         <f>SUM(K7:K51)</f>
@@ -6085,47 +6078,47 @@
       </c>
       <c r="M52" s="22">
         <f>SUM(M7:M51)</f>
-        <v>5943728.4745067004</v>
+        <v>6428977.0237200372</v>
       </c>
       <c r="N52" s="21">
         <f>SUM(N7:N51)</f>
-        <v>6300352.1829771074</v>
+        <v>6814715.6451432398</v>
       </c>
       <c r="P52" s="50"/>
     </row>
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="53">
         <f>K52-L1</f>
-        <v>517275.03995799925</v>
+        <v>-1443769.6600420019</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="188"/>
-      <c r="D54" s="188"/>
-      <c r="E54" s="188"/>
-      <c r="F54" s="188"/>
-      <c r="G54" s="188"/>
-      <c r="H54" s="188"/>
-      <c r="I54" s="188"/>
-      <c r="J54" s="188"/>
-      <c r="K54" s="188"/>
-      <c r="L54" s="188"/>
-      <c r="M54" s="188"/>
-      <c r="N54" s="188"/>
+      <c r="C54" s="211"/>
+      <c r="D54" s="211"/>
+      <c r="E54" s="211"/>
+      <c r="F54" s="211"/>
+      <c r="G54" s="211"/>
+      <c r="H54" s="211"/>
+      <c r="I54" s="211"/>
+      <c r="J54" s="211"/>
+      <c r="K54" s="211"/>
+      <c r="L54" s="211"/>
+      <c r="M54" s="211"/>
+      <c r="N54" s="211"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="188"/>
-      <c r="D55" s="188"/>
-      <c r="E55" s="188"/>
-      <c r="F55" s="188"/>
-      <c r="G55" s="188"/>
-      <c r="H55" s="188"/>
-      <c r="I55" s="188"/>
-      <c r="J55" s="188"/>
-      <c r="K55" s="188"/>
-      <c r="L55" s="188"/>
-      <c r="M55" s="188"/>
-      <c r="N55" s="188"/>
+      <c r="C55" s="211"/>
+      <c r="D55" s="211"/>
+      <c r="E55" s="211"/>
+      <c r="F55" s="211"/>
+      <c r="G55" s="211"/>
+      <c r="H55" s="211"/>
+      <c r="I55" s="211"/>
+      <c r="J55" s="211"/>
+      <c r="K55" s="211"/>
+      <c r="L55" s="211"/>
+      <c r="M55" s="211"/>
+      <c r="N55" s="211"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="70"/>
@@ -6142,111 +6135,107 @@
       <c r="N56" s="70"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="188" t="s">
+      <c r="C57" s="211" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="188"/>
-      <c r="E57" s="188"/>
-      <c r="F57" s="188"/>
-      <c r="G57" s="188"/>
-      <c r="H57" s="188"/>
-      <c r="I57" s="188"/>
-      <c r="J57" s="188"/>
-      <c r="K57" s="188"/>
-      <c r="L57" s="188"/>
-      <c r="M57" s="188"/>
-      <c r="N57" s="188"/>
+      <c r="D57" s="211"/>
+      <c r="E57" s="211"/>
+      <c r="F57" s="211"/>
+      <c r="G57" s="211"/>
+      <c r="H57" s="211"/>
+      <c r="I57" s="211"/>
+      <c r="J57" s="211"/>
+      <c r="K57" s="211"/>
+      <c r="L57" s="211"/>
+      <c r="M57" s="211"/>
+      <c r="N57" s="211"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="188"/>
-      <c r="D58" s="188"/>
-      <c r="E58" s="188"/>
-      <c r="F58" s="188"/>
-      <c r="G58" s="188"/>
-      <c r="H58" s="188"/>
-      <c r="I58" s="188"/>
-      <c r="J58" s="188"/>
-      <c r="K58" s="188"/>
-      <c r="L58" s="188"/>
-      <c r="M58" s="188"/>
-      <c r="N58" s="188"/>
+      <c r="C58" s="211"/>
+      <c r="D58" s="211"/>
+      <c r="E58" s="211"/>
+      <c r="F58" s="211"/>
+      <c r="G58" s="211"/>
+      <c r="H58" s="211"/>
+      <c r="I58" s="211"/>
+      <c r="J58" s="211"/>
+      <c r="K58" s="211"/>
+      <c r="L58" s="211"/>
+      <c r="M58" s="211"/>
+      <c r="N58" s="211"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="188"/>
-      <c r="D59" s="188"/>
-      <c r="E59" s="188"/>
-      <c r="F59" s="188"/>
-      <c r="G59" s="188"/>
-      <c r="H59" s="188"/>
-      <c r="I59" s="188"/>
-      <c r="J59" s="188"/>
-      <c r="K59" s="188"/>
-      <c r="L59" s="188"/>
-      <c r="M59" s="188"/>
-      <c r="N59" s="188"/>
+      <c r="C59" s="211"/>
+      <c r="D59" s="211"/>
+      <c r="E59" s="211"/>
+      <c r="F59" s="211"/>
+      <c r="G59" s="211"/>
+      <c r="H59" s="211"/>
+      <c r="I59" s="211"/>
+      <c r="J59" s="211"/>
+      <c r="K59" s="211"/>
+      <c r="L59" s="211"/>
+      <c r="M59" s="211"/>
+      <c r="N59" s="211"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="188"/>
-      <c r="D60" s="188"/>
-      <c r="E60" s="188"/>
-      <c r="F60" s="188"/>
-      <c r="G60" s="188"/>
-      <c r="H60" s="188"/>
-      <c r="I60" s="188"/>
-      <c r="J60" s="188"/>
-      <c r="K60" s="188"/>
-      <c r="L60" s="188"/>
-      <c r="M60" s="188"/>
-      <c r="N60" s="188"/>
+      <c r="C60" s="211"/>
+      <c r="D60" s="211"/>
+      <c r="E60" s="211"/>
+      <c r="F60" s="211"/>
+      <c r="G60" s="211"/>
+      <c r="H60" s="211"/>
+      <c r="I60" s="211"/>
+      <c r="J60" s="211"/>
+      <c r="K60" s="211"/>
+      <c r="L60" s="211"/>
+      <c r="M60" s="211"/>
+      <c r="N60" s="211"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="188"/>
-      <c r="D61" s="188"/>
-      <c r="E61" s="188"/>
-      <c r="F61" s="188"/>
-      <c r="G61" s="188"/>
-      <c r="H61" s="188"/>
-      <c r="I61" s="188"/>
-      <c r="J61" s="188"/>
-      <c r="K61" s="188"/>
-      <c r="L61" s="188"/>
-      <c r="M61" s="188"/>
-      <c r="N61" s="188"/>
+      <c r="C61" s="211"/>
+      <c r="D61" s="211"/>
+      <c r="E61" s="211"/>
+      <c r="F61" s="211"/>
+      <c r="G61" s="211"/>
+      <c r="H61" s="211"/>
+      <c r="I61" s="211"/>
+      <c r="J61" s="211"/>
+      <c r="K61" s="211"/>
+      <c r="L61" s="211"/>
+      <c r="M61" s="211"/>
+      <c r="N61" s="211"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="188"/>
-      <c r="D62" s="188"/>
-      <c r="E62" s="188"/>
-      <c r="F62" s="188"/>
-      <c r="G62" s="188"/>
-      <c r="H62" s="188"/>
-      <c r="I62" s="188"/>
-      <c r="J62" s="188"/>
-      <c r="K62" s="188"/>
-      <c r="L62" s="188"/>
-      <c r="M62" s="188"/>
-      <c r="N62" s="188"/>
+      <c r="C62" s="211"/>
+      <c r="D62" s="211"/>
+      <c r="E62" s="211"/>
+      <c r="F62" s="211"/>
+      <c r="G62" s="211"/>
+      <c r="H62" s="211"/>
+      <c r="I62" s="211"/>
+      <c r="J62" s="211"/>
+      <c r="K62" s="211"/>
+      <c r="L62" s="211"/>
+      <c r="M62" s="211"/>
+      <c r="N62" s="211"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="188"/>
-      <c r="D63" s="188"/>
-      <c r="E63" s="188"/>
-      <c r="F63" s="188"/>
-      <c r="G63" s="188"/>
-      <c r="H63" s="188"/>
-      <c r="I63" s="188"/>
-      <c r="J63" s="188"/>
-      <c r="K63" s="188"/>
-      <c r="L63" s="188"/>
-      <c r="M63" s="188"/>
-      <c r="N63" s="188"/>
+      <c r="C63" s="211"/>
+      <c r="D63" s="211"/>
+      <c r="E63" s="211"/>
+      <c r="F63" s="211"/>
+      <c r="G63" s="211"/>
+      <c r="H63" s="211"/>
+      <c r="I63" s="211"/>
+      <c r="J63" s="211"/>
+      <c r="K63" s="211"/>
+      <c r="L63" s="211"/>
+      <c r="M63" s="211"/>
+      <c r="N63" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
@@ -6261,6 +6250,10 @@
     <mergeCell ref="A1:J4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/2026/BELGRANO 1646/Junio/Junio-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Junio/Junio-BLG1646.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9B9445-F537-4846-8E86-ABB17020302D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54AD4A1-8BFF-45F4-8673-3A09B3E60513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$126</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="142">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -482,10 +482,13 @@
     <t>Sr. Gabriel Villegas - Abogado Consorcio</t>
   </si>
   <si>
-    <t>Entendiendo que en su momento, se le habia cobrado al Sr. Simonassi $3.000.000, la diferencia entre lo gastado ($6.484.614,10) y el monto mencionado se prorrateara como extraordinario en los proximos dos meses ($1.742.307)</t>
-  </si>
-  <si>
     <t>Gasto abonado por Sr. Nestor Campana : Reparación de superficie dañada por filtración y pintura en dormitorio con materiales incluídos.</t>
+  </si>
+  <si>
+    <t>Convenio de pago sindicato abogado Maximiliano Oliver</t>
+  </si>
+  <si>
+    <t>Entendiendo que en su momento, se le habia cobrado al Sr. Simonassi $3.000.000, la diferencia entre lo gastado ($6.579.071,62) y el monto mencionado se prorrateara como extraordinario en los proximos dos meses ($1.789.535)</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1078,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1283,6 +1286,25 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1354,12 +1376,6 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1369,8 +1385,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1441,16 +1460,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1850,7 +1859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -1869,13 +1878,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="90"/>
-      <c r="B1" s="157" t="s">
+      <c r="B1" s="164" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="158"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="165"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
@@ -1979,29 +1988,29 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="78"/>
-      <c r="B14" s="161" t="s">
+      <c r="B14" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="162"/>
-      <c r="D14" s="163"/>
+      <c r="C14" s="169"/>
+      <c r="D14" s="170"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="78"/>
-      <c r="B15" s="164"/>
-      <c r="C15" s="165"/>
-      <c r="D15" s="166"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="173"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="78"/>
-      <c r="B16" s="164"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="166"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="172"/>
+      <c r="D16" s="173"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="78"/>
-      <c r="B17" s="167"/>
-      <c r="C17" s="168"/>
-      <c r="D17" s="169"/>
+      <c r="B17" s="174"/>
+      <c r="C17" s="175"/>
+      <c r="D17" s="176"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="78"/>
@@ -2808,11 +2817,11 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="187" t="s">
-        <v>140</v>
-      </c>
-      <c r="B60" s="182"/>
-      <c r="C60" s="183"/>
+      <c r="A60" s="161" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="162"/>
+      <c r="C60" s="163"/>
       <c r="D60" s="37">
         <v>278000</v>
       </c>
@@ -2830,11 +2839,11 @@
       <c r="J60" s="76"/>
     </row>
     <row r="61" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="184" t="s">
+      <c r="A61" s="189" t="s">
         <v>130</v>
       </c>
-      <c r="B61" s="185"/>
-      <c r="C61" s="186"/>
+      <c r="B61" s="190"/>
+      <c r="C61" s="191"/>
       <c r="D61" s="37">
         <v>152940</v>
       </c>
@@ -2858,11 +2867,11 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="187" t="s">
+      <c r="A62" s="161" t="s">
         <v>129</v>
       </c>
-      <c r="B62" s="182"/>
-      <c r="C62" s="183"/>
+      <c r="B62" s="162"/>
+      <c r="C62" s="163"/>
       <c r="D62" s="37">
         <v>65000</v>
       </c>
@@ -2886,11 +2895,11 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="187" t="s">
+      <c r="A63" s="161" t="s">
         <v>129</v>
       </c>
-      <c r="B63" s="182"/>
-      <c r="C63" s="183"/>
+      <c r="B63" s="162"/>
+      <c r="C63" s="163"/>
       <c r="D63" s="37">
         <v>41000</v>
       </c>
@@ -2947,9 +2956,9 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="181"/>
-      <c r="B65" s="182"/>
-      <c r="C65" s="183"/>
+      <c r="A65" s="188"/>
+      <c r="B65" s="162"/>
+      <c r="C65" s="163"/>
       <c r="D65" s="37"/>
       <c r="E65" s="60">
         <f t="shared" si="21"/>
@@ -3251,15 +3260,16 @@
       <c r="B82" s="79"/>
       <c r="C82" s="79"/>
       <c r="D82" s="37">
-        <v>180218.02</v>
+        <f>152+180218.02</f>
+        <v>180370.02</v>
       </c>
       <c r="E82" s="60">
         <f>D82*91.91%</f>
-        <v>165638.38218199997</v>
+        <v>165778.08538199996</v>
       </c>
       <c r="F82" s="49">
         <f>D82*8.09%</f>
-        <v>14579.637817999999</v>
+        <v>14591.934617999999</v>
       </c>
       <c r="H82" s="61"/>
     </row>
@@ -3290,19 +3300,19 @@
       <c r="C84" s="118"/>
       <c r="D84" s="64">
         <f>SUM(D82:D83)</f>
-        <v>249218.02</v>
+        <v>249370.02</v>
       </c>
       <c r="E84" s="58">
         <f t="shared" ref="E84:F84" si="22">SUM(E82:E83)</f>
-        <v>229056.28218199997</v>
+        <v>229195.98538199996</v>
       </c>
       <c r="F84" s="58">
         <f t="shared" si="22"/>
-        <v>20161.737818000001</v>
+        <v>20174.034617999998</v>
       </c>
       <c r="G84" s="34">
         <f>E84+F84</f>
-        <v>249218.01999999996</v>
+        <v>249370.01999999996</v>
       </c>
       <c r="H84" s="61" t="str">
         <f>IF(D84=G84, "", "Error")</f>
@@ -3360,19 +3370,19 @@
       <c r="C88" s="135"/>
       <c r="D88" s="80">
         <f>SUM(D86+D84+D80+D73+D66+D47+D32+D27+D42)</f>
-        <v>8819682.2200000007</v>
+        <v>8819834.2200000007</v>
       </c>
       <c r="E88" s="59">
         <f>SUM(E86+E84+E80+E73+E66+E47+E32+E27+E42)</f>
-        <v>8330246.7564919991</v>
+        <v>8330386.4596919995</v>
       </c>
       <c r="F88" s="148">
         <f>SUM(F27+F42+F47+F66+F73+F80+F84+F86)</f>
-        <v>489435.46350800002</v>
+        <v>489447.76030799997</v>
       </c>
       <c r="G88" s="34">
         <f>E88+F88</f>
-        <v>8819682.2199999988</v>
+        <v>8819834.2199999988</v>
       </c>
       <c r="H88" s="61" t="str">
         <f>IF(D88=G88, "", "Error")</f>
@@ -3429,12 +3439,12 @@
       <c r="E95" s="52"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="176" t="s">
+      <c r="A96" s="183" t="s">
         <v>85</v>
       </c>
-      <c r="B96" s="177"/>
-      <c r="C96" s="177"/>
-      <c r="D96" s="177"/>
+      <c r="B96" s="184"/>
+      <c r="C96" s="184"/>
+      <c r="D96" s="184"/>
       <c r="E96" s="73" t="s">
         <v>19</v>
       </c>
@@ -3443,29 +3453,29 @@
       </c>
     </row>
     <row r="97" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A97" s="173" t="s">
+      <c r="A97" s="180" t="s">
         <v>135</v>
       </c>
-      <c r="B97" s="174"/>
-      <c r="C97" s="175"/>
+      <c r="B97" s="181"/>
+      <c r="C97" s="182"/>
       <c r="D97" s="37">
         <v>4000000</v>
       </c>
       <c r="E97" s="60">
-        <f t="shared" ref="E97:E100" si="23">D97*91.91%</f>
+        <f t="shared" ref="E97:E101" si="23">D97*91.91%</f>
         <v>3676399.9999999995</v>
       </c>
       <c r="F97" s="49">
-        <f t="shared" ref="F97:F100" si="24">D97*8.09%</f>
+        <f t="shared" ref="F97:F101" si="24">D97*8.09%</f>
         <v>323600</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="178" t="s">
+      <c r="A98" s="185" t="s">
         <v>136</v>
       </c>
-      <c r="B98" s="179"/>
-      <c r="C98" s="180"/>
+      <c r="B98" s="186"/>
+      <c r="C98" s="187"/>
       <c r="D98" s="37">
         <v>891000</v>
       </c>
@@ -3479,340 +3489,357 @@
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="212" t="s">
-        <v>138</v>
-      </c>
-      <c r="B99" s="155"/>
-      <c r="C99" s="156"/>
+      <c r="A99" s="159" t="s">
+        <v>140</v>
+      </c>
+      <c r="B99" s="157"/>
+      <c r="C99" s="158"/>
       <c r="D99" s="37">
-        <v>880000</v>
+        <v>94457.62</v>
       </c>
       <c r="E99" s="60">
         <f t="shared" si="23"/>
-        <v>808807.99999999988</v>
+        <v>86815.998541999987</v>
       </c>
       <c r="F99" s="49">
         <f t="shared" si="24"/>
-        <v>71192</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="178" t="s">
-        <v>137</v>
-      </c>
-      <c r="B100" s="179"/>
-      <c r="C100" s="180"/>
+        <v>7641.6214579999996</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="159" t="s">
+        <v>138</v>
+      </c>
+      <c r="B100" s="155"/>
+      <c r="C100" s="156"/>
       <c r="D100" s="37">
-        <v>713614</v>
+        <v>880000</v>
       </c>
       <c r="E100" s="60">
         <f t="shared" si="23"/>
-        <v>655882.6274</v>
+        <v>808807.99999999988</v>
       </c>
       <c r="F100" s="49">
         <f t="shared" si="24"/>
+        <v>71192</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="185" t="s">
+        <v>137</v>
+      </c>
+      <c r="B101" s="186"/>
+      <c r="C101" s="187"/>
+      <c r="D101" s="37">
+        <v>713614</v>
+      </c>
+      <c r="E101" s="60">
+        <f t="shared" si="23"/>
+        <v>655882.6274</v>
+      </c>
+      <c r="F101" s="49">
+        <f t="shared" si="24"/>
         <v>57731.372600000002</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="170" t="s">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="B101" s="171"/>
-      <c r="C101" s="172"/>
-      <c r="D101" s="72">
-        <f>SUM(D97:D100)</f>
-        <v>6484614</v>
-      </c>
-      <c r="E101" s="72">
-        <f>SUM(E97:E100)</f>
-        <v>5960008.7273999993</v>
-      </c>
-      <c r="F101" s="72">
-        <f>SUM(F97:F100)</f>
-        <v>524605.27260000003</v>
-      </c>
-      <c r="H101" s="34">
-        <f>E101+F101</f>
-        <v>6484613.9999999991</v>
-      </c>
-      <c r="I101" s="61" t="str">
-        <f>IF(D101=H101, "", "Error")</f>
+      <c r="B102" s="178"/>
+      <c r="C102" s="179"/>
+      <c r="D102" s="72">
+        <f>SUM(D97:D101)</f>
+        <v>6579071.6200000001</v>
+      </c>
+      <c r="E102" s="72">
+        <f>SUM(E97:E101)</f>
+        <v>6046824.7259419989</v>
+      </c>
+      <c r="F102" s="72">
+        <f>SUM(F97:F101)</f>
+        <v>532246.89405800006</v>
+      </c>
+      <c r="H102" s="34">
+        <f>E102+F102</f>
+        <v>6579071.6199999992</v>
+      </c>
+      <c r="I102" s="61" t="str">
+        <f>IF(D102=H102, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D102" s="34"/>
-    </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="213" t="s">
-        <v>139</v>
-      </c>
-      <c r="B103" s="213"/>
-      <c r="C103" s="213"/>
-      <c r="D103" s="213"/>
-      <c r="E103" s="213"/>
-      <c r="F103" s="213"/>
+      <c r="D103" s="34"/>
+      <c r="H103" s="34"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="213"/>
-      <c r="B104" s="213"/>
-      <c r="C104" s="213"/>
-      <c r="D104" s="213"/>
-      <c r="E104" s="213"/>
-      <c r="F104" s="213"/>
+      <c r="A104" s="192" t="s">
+        <v>141</v>
+      </c>
+      <c r="B104" s="192"/>
+      <c r="C104" s="192"/>
+      <c r="D104" s="192"/>
+      <c r="E104" s="192"/>
+      <c r="F104" s="192"/>
+      <c r="H104" s="34"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="213"/>
-      <c r="B105" s="213"/>
-      <c r="C105" s="213"/>
-      <c r="D105" s="213"/>
-      <c r="E105" s="213"/>
-      <c r="F105" s="213"/>
+      <c r="A105" s="192"/>
+      <c r="B105" s="192"/>
+      <c r="C105" s="192"/>
+      <c r="D105" s="192"/>
+      <c r="E105" s="192"/>
+      <c r="F105" s="192"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="213"/>
-      <c r="B106" s="213"/>
-      <c r="C106" s="213"/>
-      <c r="D106" s="213"/>
-      <c r="E106" s="213"/>
-      <c r="F106" s="213"/>
-    </row>
-    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E107" s="34"/>
+      <c r="A106" s="192"/>
+      <c r="B106" s="192"/>
+      <c r="C106" s="192"/>
+      <c r="D106" s="192"/>
+      <c r="E106" s="192"/>
+      <c r="F106" s="192"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="192"/>
+      <c r="B107" s="192"/>
+      <c r="C107" s="192"/>
+      <c r="D107" s="192"/>
+      <c r="E107" s="192"/>
+      <c r="F107" s="192"/>
     </row>
     <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="28" t="s">
+      <c r="E108" s="34"/>
+    </row>
+    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="B108" s="29">
+      <c r="B109" s="29">
         <f>D88</f>
-        <v>8819682.2200000007</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="30" t="s">
+        <v>8819834.2200000007</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B109" s="31">
+      <c r="B110" s="31">
         <f>D88-D86</f>
-        <v>8819682.2200000007</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D110" s="160"/>
-      <c r="E110" s="160"/>
+        <v>8819834.2200000007</v>
+      </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="9" t="s">
+      <c r="D111" s="167"/>
+      <c r="E111" s="167"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B111" s="10"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="160"/>
-      <c r="E111" s="160"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="12" t="s">
+      <c r="B112" s="10"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="167"/>
+      <c r="E112" s="167"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B112" s="5">
+      <c r="B113" s="5">
         <v>14089108.26</v>
       </c>
-      <c r="C112" s="13"/>
-      <c r="D112" s="160"/>
-      <c r="E112" s="160"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="14" t="s">
+      <c r="C113" s="13"/>
+      <c r="D113" s="167"/>
+      <c r="E113" s="167"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B113" s="23">
+      <c r="B114" s="23">
         <f>PRORRATEO!G52</f>
         <v>8666282.7266246639</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C114" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D113" s="160"/>
-      <c r="E113" s="160"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B114" s="75">
-        <f>-B109</f>
-        <v>-8819682.2200000007</v>
-      </c>
-      <c r="C114" s="11"/>
-      <c r="D114" s="160"/>
-      <c r="E114" s="160"/>
-      <c r="G114" s="37"/>
+      <c r="D114" s="167"/>
+      <c r="E114" s="167"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B115" s="75">
-        <f>-D101</f>
-        <v>-6484614</v>
+        <f>-B110</f>
+        <v>-8819834.2200000007</v>
       </c>
       <c r="C115" s="11"/>
-      <c r="D115" s="160"/>
-      <c r="E115" s="160"/>
-      <c r="G115" s="43"/>
+      <c r="D115" s="167"/>
+      <c r="E115" s="167"/>
+      <c r="G115" s="37"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B116" s="75">
-        <f>-B122</f>
-        <v>0</v>
-      </c>
-      <c r="C116" s="15"/>
+        <f>-D102</f>
+        <v>-6579071.6200000001</v>
+      </c>
+      <c r="C116" s="11"/>
+      <c r="D116" s="167"/>
+      <c r="E116" s="167"/>
+      <c r="G116" s="43"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B117" s="75">
+        <f>-B123</f>
+        <v>0</v>
+      </c>
+      <c r="C117" s="15"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B117" s="24">
+      <c r="B118" s="24">
         <f>-C93</f>
         <v>0</v>
       </c>
-      <c r="C117" s="15"/>
-      <c r="E117" s="34"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="12" t="s">
+      <c r="C118" s="15"/>
+      <c r="E118" s="34"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B118" s="16">
-        <f>SUM(B112:B117)</f>
-        <v>7451094.7666246649</v>
-      </c>
-      <c r="C118" s="62">
-        <f>7273784-B125-B118</f>
-        <v>-94616.226624664851</v>
-      </c>
-      <c r="D118" s="34"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="15"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="18"/>
+      <c r="B119" s="16">
+        <f>SUM(B113:B118)</f>
+        <v>7356485.1466246648</v>
+      </c>
+      <c r="C119" s="62"/>
+      <c r="D119" s="34"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="15"/>
       <c r="C120" s="11"/>
-      <c r="D120" s="34"/>
-      <c r="E120" s="76"/>
+      <c r="D120" s="18"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="9" t="s">
+      <c r="C121" s="11"/>
+      <c r="D121" s="34"/>
+      <c r="E121" s="76"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B121" s="86">
+      <c r="B122" s="86">
         <f>-82694.54</f>
         <v>-82694.539999999994</v>
       </c>
-      <c r="C121" s="17"/>
-      <c r="D121" s="76"/>
-      <c r="E121" s="76"/>
-      <c r="F121" s="76"/>
-    </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B122" s="24">
-        <v>0</v>
-      </c>
       <c r="C122" s="17"/>
       <c r="D122" s="76"/>
-      <c r="E122" s="81"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="12"/>
-      <c r="B123" s="75"/>
+      <c r="E122" s="76"/>
+      <c r="F122" s="76"/>
+    </row>
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" s="24">
+        <v>0</v>
+      </c>
       <c r="C123" s="17"/>
-      <c r="E123" s="34"/>
+      <c r="D123" s="76"/>
+      <c r="E123" s="81"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="12"/>
       <c r="B124" s="75"/>
       <c r="C124" s="17"/>
-      <c r="D124" s="138"/>
       <c r="E124" s="34"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="26" t="s">
+      <c r="A125" s="12"/>
+      <c r="B125" s="75"/>
+      <c r="C125" s="17"/>
+      <c r="D125" s="138"/>
+      <c r="E125" s="34"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B125" s="27">
-        <f>SUM(B121:B124)</f>
+      <c r="B126" s="27">
+        <f>SUM(B122:B125)</f>
         <v>-82694.539999999994</v>
       </c>
-      <c r="C125" s="17"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C126" s="18"/>
-      <c r="D126" s="76"/>
+      <c r="C126" s="17"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B127" s="15"/>
-      <c r="C127" s="11"/>
-    </row>
-    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N129" s="6"/>
-    </row>
-    <row r="132" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B132" s="159"/>
-      <c r="C132" s="159"/>
-      <c r="D132" s="159"/>
-      <c r="E132" s="159"/>
+      <c r="C127" s="18"/>
+      <c r="D127" s="76"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B128" s="15"/>
+      <c r="C128" s="11"/>
+    </row>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N130" s="6"/>
     </row>
     <row r="133" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B133" s="159"/>
-      <c r="C133" s="159"/>
-      <c r="D133" s="159"/>
-      <c r="E133" s="159"/>
+      <c r="B133" s="166"/>
+      <c r="C133" s="166"/>
+      <c r="D133" s="166"/>
+      <c r="E133" s="166"/>
     </row>
     <row r="134" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B134" s="159"/>
-      <c r="C134" s="159"/>
-      <c r="D134" s="159"/>
-      <c r="E134" s="159"/>
+      <c r="B134" s="166"/>
+      <c r="C134" s="166"/>
+      <c r="D134" s="166"/>
+      <c r="E134" s="166"/>
     </row>
     <row r="135" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B135" s="159"/>
-      <c r="C135" s="159"/>
-      <c r="D135" s="159"/>
-      <c r="E135" s="159"/>
+      <c r="B135" s="166"/>
+      <c r="C135" s="166"/>
+      <c r="D135" s="166"/>
+      <c r="E135" s="166"/>
     </row>
     <row r="136" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B136" s="159"/>
-      <c r="C136" s="159"/>
-      <c r="D136" s="159"/>
-      <c r="E136" s="159"/>
+      <c r="B136" s="166"/>
+      <c r="C136" s="166"/>
+      <c r="D136" s="166"/>
+      <c r="E136" s="166"/>
+    </row>
+    <row r="137" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B137" s="166"/>
+      <c r="C137" s="166"/>
+      <c r="D137" s="166"/>
+      <c r="E137" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B132:E136"/>
-    <mergeCell ref="D110:E115"/>
+    <mergeCell ref="B133:E137"/>
+    <mergeCell ref="D111:E116"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A102:C102"/>
     <mergeCell ref="A97:C97"/>
     <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A101:C101"/>
     <mergeCell ref="A65:C65"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A103:F106"/>
+    <mergeCell ref="A104:F107"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3844,44 +3871,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="205" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 17/07</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="201"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="207"/>
       <c r="K1" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="188">
+      <c r="L1" s="194">
         <f>RESUMEN!D88</f>
-        <v>8819682.2200000007</v>
-      </c>
-      <c r="M1" s="189"/>
+        <v>8819834.2200000007</v>
+      </c>
+      <c r="M1" s="195"/>
       <c r="N1" s="91"/>
       <c r="O1" s="50">
         <f>L1*8.09%</f>
-        <v>713512.2915980001</v>
+        <v>713524.58839800011</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="202"/>
-      <c r="B2" s="203"/>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
-      <c r="J2" s="204"/>
+      <c r="A2" s="208"/>
+      <c r="B2" s="209"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="209"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="209"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="209"/>
+      <c r="I2" s="209"/>
+      <c r="J2" s="210"/>
       <c r="K2" s="92" t="s">
         <v>95</v>
       </c>
@@ -3893,114 +3920,114 @@
       <c r="N2" s="94"/>
       <c r="O2" s="50">
         <f>O1-K7-553-50-86-8</f>
-        <v>402392.0716400001</v>
+        <v>402404.36844000011</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="202"/>
-      <c r="B3" s="203"/>
-      <c r="C3" s="203"/>
-      <c r="D3" s="203"/>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="203"/>
-      <c r="I3" s="203"/>
-      <c r="J3" s="204"/>
+      <c r="A3" s="208"/>
+      <c r="B3" s="209"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="209"/>
+      <c r="E3" s="209"/>
+      <c r="F3" s="209"/>
+      <c r="G3" s="209"/>
+      <c r="H3" s="209"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="210"/>
       <c r="K3" s="92" t="s">
         <v>100</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="95">
-        <f>RESUMEN!D101</f>
-        <v>6484614</v>
+        <f>RESUMEN!D102</f>
+        <v>6579071.6200000001</v>
       </c>
       <c r="N3" s="96"/>
       <c r="O3" s="8"/>
     </row>
     <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="205"/>
-      <c r="B4" s="206"/>
-      <c r="C4" s="206"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="206"/>
-      <c r="F4" s="206"/>
-      <c r="G4" s="206"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="206"/>
-      <c r="J4" s="207"/>
+      <c r="A4" s="211"/>
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="213"/>
       <c r="K4" s="97" t="s">
         <v>95</v>
       </c>
       <c r="L4" s="98"/>
       <c r="M4" s="99">
-        <v>1742307</v>
+        <v>1789535.8099999996</v>
       </c>
       <c r="N4" s="100"/>
       <c r="O4" s="50">
         <f>M3/3</f>
-        <v>2161538</v>
+        <v>2193023.8733333335</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="192" t="s">
+      <c r="A5" s="198" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="208" t="s">
+      <c r="B5" s="214" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="198" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="197" t="s">
+      <c r="D5" s="203" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="192" t="s">
+      <c r="E5" s="198" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="192" t="s">
+      <c r="F5" s="198" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="192" t="s">
+      <c r="G5" s="198" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="194" t="s">
+      <c r="H5" s="200" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="197" t="s">
+      <c r="I5" s="203" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="190" t="s">
+      <c r="J5" s="196" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="190" t="s">
+      <c r="K5" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="190" t="s">
+      <c r="L5" s="196" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="190" t="s">
+      <c r="M5" s="196" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="190" t="s">
+      <c r="N5" s="196" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="193"/>
-      <c r="B6" s="209"/>
-      <c r="C6" s="193"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="193"/>
-      <c r="F6" s="193"/>
-      <c r="G6" s="193"/>
-      <c r="H6" s="195"/>
-      <c r="I6" s="198"/>
-      <c r="J6" s="196"/>
-      <c r="K6" s="191"/>
-      <c r="L6" s="196"/>
-      <c r="M6" s="191"/>
-      <c r="N6" s="191"/>
+      <c r="A6" s="199"/>
+      <c r="B6" s="215"/>
+      <c r="C6" s="199"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="199"/>
+      <c r="F6" s="199"/>
+      <c r="G6" s="199"/>
+      <c r="H6" s="201"/>
+      <c r="I6" s="204"/>
+      <c r="J6" s="202"/>
+      <c r="K6" s="197"/>
+      <c r="L6" s="202"/>
+      <c r="M6" s="197"/>
+      <c r="N6" s="197"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -4032,7 +4059,7 @@
       </c>
       <c r="J7" s="19">
         <f>M$4*E7%</f>
-        <v>140952.63630000001</v>
+        <v>144773.44702899997</v>
       </c>
       <c r="K7" s="19">
         <v>310423.219958</v>
@@ -4040,11 +4067,11 @@
       <c r="L7" s="25"/>
       <c r="M7" s="2">
         <f>K7+J7+H7+L7</f>
-        <v>451375.85625800001</v>
+        <v>455196.66698699998</v>
       </c>
       <c r="N7" s="5">
         <f>M7*6% + M7</f>
-        <v>478458.40763348003</v>
+        <v>482508.46700621996</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4076,7 +4103,7 @@
       </c>
       <c r="J8" s="19">
         <f>M$4*E8%</f>
-        <v>38504.984699999994</v>
+        <v>39548.741400999985</v>
       </c>
       <c r="K8" s="19">
         <f>M$2*E8 /100</f>
@@ -4085,11 +4112,11 @@
       <c r="L8" s="88"/>
       <c r="M8" s="2">
         <f>K8+J8+H8+L8</f>
-        <v>195961.00153118256</v>
+        <v>197004.75823218253</v>
       </c>
       <c r="N8" s="5">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>207718.66162305351</v>
+        <v>208825.04372611348</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -4122,7 +4149,7 @@
       </c>
       <c r="J9" s="19">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
-        <v>73351.1247</v>
+        <v>75339.457600999987</v>
       </c>
       <c r="K9" s="19">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
@@ -4131,11 +4158,11 @@
       <c r="L9" s="88"/>
       <c r="M9" s="2">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>396990.76756759669</v>
+        <v>398979.10046859668</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" si="1"/>
-        <v>420810.21362165251</v>
+        <v>422917.84649671247</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -4167,7 +4194,7 @@
       </c>
       <c r="J10" s="19">
         <f t="shared" si="2"/>
-        <v>49481.518799999998</v>
+        <v>50822.817003999982</v>
       </c>
       <c r="K10" s="19">
         <f t="shared" si="3"/>
@@ -4176,11 +4203,11 @@
       <c r="L10" s="88"/>
       <c r="M10" s="2">
         <f t="shared" si="4"/>
-        <v>291603.83880000003</v>
+        <v>292945.13700400002</v>
       </c>
       <c r="N10" s="5">
         <f t="shared" si="1"/>
-        <v>309100.069128</v>
+        <v>310521.84522424004</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -4213,7 +4240,7 @@
       </c>
       <c r="J11" s="19">
         <f t="shared" si="2"/>
-        <v>59761.130100000009</v>
+        <v>61381.078282999995</v>
       </c>
       <c r="K11" s="19">
         <f t="shared" si="3"/>
@@ -4222,11 +4249,11 @@
       <c r="L11" s="88"/>
       <c r="M11" s="2">
         <f t="shared" si="4"/>
-        <v>323438.95010000002</v>
+        <v>325058.89828299999</v>
       </c>
       <c r="N11" s="5">
         <f t="shared" si="1"/>
-        <v>342845.287106</v>
+        <v>344562.43217997998</v>
       </c>
       <c r="P11" s="34"/>
     </row>
@@ -4260,7 +4287,7 @@
       </c>
       <c r="J12" s="19">
         <f t="shared" si="2"/>
-        <v>49481.518799999998</v>
+        <v>50822.817003999982</v>
       </c>
       <c r="K12" s="19">
         <f t="shared" si="3"/>
@@ -4269,11 +4296,11 @@
       <c r="L12" s="88"/>
       <c r="M12" s="2">
         <f t="shared" si="4"/>
-        <v>267803.67879999999</v>
+        <v>269144.97700399999</v>
       </c>
       <c r="N12" s="5">
         <f t="shared" si="1"/>
-        <v>283871.89952799998</v>
+        <v>285293.67562423996</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -4306,7 +4333,7 @@
       </c>
       <c r="J13" s="19">
         <f t="shared" si="2"/>
-        <v>59761.130100000009</v>
+        <v>61381.078282999995</v>
       </c>
       <c r="K13" s="19">
         <f t="shared" si="3"/>
@@ -4315,11 +4342,11 @@
       <c r="L13" s="88"/>
       <c r="M13" s="2">
         <f t="shared" si="4"/>
-        <v>323438.24751924182</v>
+        <v>325058.19570224179</v>
       </c>
       <c r="N13" s="5">
         <f t="shared" si="1"/>
-        <v>342844.54237039632</v>
+        <v>344561.68744437629</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -4351,7 +4378,7 @@
       </c>
       <c r="J14" s="19">
         <f t="shared" si="2"/>
-        <v>49481.518799999998</v>
+        <v>50822.817003999982</v>
       </c>
       <c r="K14" s="19">
         <f t="shared" si="3"/>
@@ -4360,11 +4387,11 @@
       <c r="L14" s="88"/>
       <c r="M14" s="2">
         <f t="shared" si="4"/>
-        <v>637988.65934666665</v>
+        <v>639329.95755066664</v>
       </c>
       <c r="N14" s="5">
         <f t="shared" si="1"/>
-        <v>676267.97890746663</v>
+        <v>677689.75500370667</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -4397,7 +4424,7 @@
       </c>
       <c r="J15" s="19">
         <f t="shared" si="2"/>
-        <v>59761.130100000009</v>
+        <v>61381.078282999995</v>
       </c>
       <c r="K15" s="19">
         <f t="shared" si="3"/>
@@ -4406,11 +4433,11 @@
       <c r="L15" s="88"/>
       <c r="M15" s="2">
         <f t="shared" si="4"/>
-        <v>323438.83335632621</v>
+        <v>325058.78153932618</v>
       </c>
       <c r="N15" s="5">
         <f t="shared" si="1"/>
-        <v>342845.16335770581</v>
+        <v>344562.30843168573</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -4443,7 +4470,7 @@
       </c>
       <c r="J16" s="19">
         <f t="shared" si="2"/>
-        <v>49481.518799999998</v>
+        <v>50822.817003999982</v>
       </c>
       <c r="K16" s="19">
         <f t="shared" si="3"/>
@@ -4452,11 +4479,11 @@
       <c r="L16" s="88"/>
       <c r="M16" s="2">
         <f t="shared" si="4"/>
-        <v>267804.17862700007</v>
+        <v>269145.47683100007</v>
       </c>
       <c r="N16" s="5">
         <f t="shared" si="1"/>
-        <v>283872.42934462009</v>
+        <v>285294.20544086007</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -4489,7 +4516,7 @@
       </c>
       <c r="J17" s="19">
         <f t="shared" si="2"/>
-        <v>59761.130100000009</v>
+        <v>61381.078282999995</v>
       </c>
       <c r="K17" s="19">
         <f t="shared" si="3"/>
@@ -4498,11 +4525,11 @@
       <c r="L17" s="88"/>
       <c r="M17" s="2">
         <f t="shared" si="4"/>
-        <v>318872.82588511507</v>
+        <v>320492.77406811505</v>
       </c>
       <c r="N17" s="5">
         <f t="shared" si="1"/>
-        <v>338005.19543822197</v>
+        <v>339722.34051220195</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -4535,7 +4562,7 @@
       </c>
       <c r="J18" s="19">
         <f t="shared" si="2"/>
-        <v>49481.518799999998</v>
+        <v>50822.817003999982</v>
       </c>
       <c r="K18" s="19">
         <f t="shared" si="3"/>
@@ -4544,11 +4571,11 @@
       <c r="L18" s="88"/>
       <c r="M18" s="2">
         <f t="shared" si="4"/>
-        <v>267779.52259991795</v>
+        <v>269120.82080391794</v>
       </c>
       <c r="N18" s="5">
         <f t="shared" si="1"/>
-        <v>283846.29395591305</v>
+        <v>285268.07005215302</v>
       </c>
       <c r="P18" t="s">
         <v>111</v>
@@ -4584,7 +4611,7 @@
       </c>
       <c r="J19" s="19">
         <f t="shared" si="2"/>
-        <v>59761.130100000009</v>
+        <v>61381.078282999995</v>
       </c>
       <c r="K19" s="19">
         <f t="shared" si="3"/>
@@ -4593,11 +4620,11 @@
       <c r="L19" s="88"/>
       <c r="M19" s="2">
         <f t="shared" si="4"/>
-        <v>323438.54974850151</v>
+        <v>325058.49793150148</v>
       </c>
       <c r="N19" s="5">
         <f t="shared" si="1"/>
-        <v>342844.8627334116</v>
+        <v>344562.00780739158</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -4630,7 +4657,7 @@
       </c>
       <c r="J20" s="19">
         <f t="shared" si="2"/>
-        <v>49481.518799999998</v>
+        <v>50822.817003999982</v>
       </c>
       <c r="K20" s="19">
         <f t="shared" si="3"/>
@@ -4639,11 +4666,11 @@
       <c r="L20" s="88"/>
       <c r="M20" s="2">
         <f t="shared" si="4"/>
-        <v>267803.75465707469</v>
+        <v>269145.05286107468</v>
       </c>
       <c r="N20" s="5">
         <f t="shared" si="1"/>
-        <v>283871.97993649915</v>
+        <v>285293.75603273918</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4676,7 +4703,7 @@
       </c>
       <c r="J21" s="19">
         <f t="shared" si="2"/>
-        <v>59761.130100000009</v>
+        <v>61381.078282999995</v>
       </c>
       <c r="K21" s="19">
         <f t="shared" si="3"/>
@@ -4685,11 +4712,11 @@
       <c r="L21" s="88"/>
       <c r="M21" s="2">
         <f t="shared" si="4"/>
-        <v>323438.72539363714</v>
+        <v>325058.67357663711</v>
       </c>
       <c r="N21" s="5">
         <f t="shared" si="1"/>
-        <v>342845.04891725536</v>
+        <v>344562.19399123534</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4722,7 +4749,7 @@
       </c>
       <c r="J22" s="19">
         <f t="shared" si="2"/>
-        <v>49481.518799999998</v>
+        <v>50822.817003999982</v>
       </c>
       <c r="K22" s="19">
         <f t="shared" si="3"/>
@@ -4731,11 +4758,11 @@
       <c r="L22" s="88"/>
       <c r="M22" s="2">
         <f t="shared" si="4"/>
-        <v>267803.67879999999</v>
+        <v>269144.97700399999</v>
       </c>
       <c r="N22" s="5">
         <f t="shared" si="1"/>
-        <v>283871.89952799998</v>
+        <v>285293.67562423996</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -4768,7 +4795,7 @@
       </c>
       <c r="J23" s="19">
         <f t="shared" si="2"/>
-        <v>59761.130100000009</v>
+        <v>61381.078282999995</v>
       </c>
       <c r="K23" s="19">
         <f t="shared" si="3"/>
@@ -4777,11 +4804,11 @@
       <c r="L23" s="88"/>
       <c r="M23" s="2">
         <f t="shared" si="4"/>
-        <v>283802.43800342228</v>
+        <v>285422.38618642226</v>
       </c>
       <c r="N23" s="5">
         <f t="shared" si="1"/>
-        <v>300830.58428362763</v>
+        <v>302547.7293576076</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4814,7 +4841,7 @@
       </c>
       <c r="J24" s="19">
         <f t="shared" si="2"/>
-        <v>49481.518799999998</v>
+        <v>50822.817003999982</v>
       </c>
       <c r="K24" s="19">
         <f t="shared" si="3"/>
@@ -4823,11 +4850,11 @@
       <c r="L24" s="88"/>
       <c r="M24" s="2">
         <f t="shared" si="4"/>
-        <v>267803.47222107474</v>
+        <v>269144.77042507473</v>
       </c>
       <c r="N24" s="5">
         <f t="shared" si="1"/>
-        <v>283871.6805543392</v>
+        <v>285293.45665057923</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -4860,7 +4887,7 @@
       </c>
       <c r="J25" s="19">
         <f t="shared" si="2"/>
-        <v>59761.130100000009</v>
+        <v>61381.078282999995</v>
       </c>
       <c r="K25" s="19">
         <f t="shared" si="3"/>
@@ -4869,11 +4896,11 @@
       <c r="L25" s="89"/>
       <c r="M25" s="2">
         <f t="shared" si="4"/>
-        <v>323438.95010000002</v>
+        <v>325058.89828299999</v>
       </c>
       <c r="N25" s="5">
         <f t="shared" si="1"/>
-        <v>342845.287106</v>
+        <v>344562.43217997998</v>
       </c>
       <c r="P25" s="53"/>
       <c r="Q25" s="53"/>
@@ -4909,7 +4936,7 @@
       </c>
       <c r="J26" s="19">
         <f t="shared" si="2"/>
-        <v>104538.42</v>
+        <v>107372.14859999997</v>
       </c>
       <c r="K26" s="19">
         <f t="shared" si="3"/>
@@ -4918,11 +4945,11 @@
       <c r="L26" s="88"/>
       <c r="M26" s="2">
         <f t="shared" si="4"/>
-        <v>-2459255.2606672961</v>
+        <v>-2456421.5320672961</v>
       </c>
       <c r="N26" s="5">
         <f t="shared" si="1"/>
-        <v>-2606810.576307334</v>
+        <v>-2603806.8239913341</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -4955,7 +4982,7 @@
       </c>
       <c r="J27" s="19">
         <f t="shared" si="2"/>
-        <v>102621.88229999998</v>
+        <v>105403.65920899996</v>
       </c>
       <c r="K27" s="19">
         <f t="shared" si="3"/>
@@ -4964,11 +4991,11 @@
       <c r="L27" s="88"/>
       <c r="M27" s="2">
         <f t="shared" si="4"/>
-        <v>555521.81358526531</v>
+        <v>558303.59049426531</v>
       </c>
       <c r="N27" s="5">
         <f t="shared" si="1"/>
-        <v>588853.12240038125</v>
+        <v>591801.80592392129</v>
       </c>
       <c r="R27" s="53"/>
     </row>
@@ -5002,7 +5029,7 @@
       </c>
       <c r="J28" s="19">
         <f t="shared" si="2"/>
-        <v>102621.88229999998</v>
+        <v>105403.65920899996</v>
       </c>
       <c r="K28" s="19">
         <f t="shared" si="3"/>
@@ -5011,11 +5038,11 @@
       <c r="L28" s="88"/>
       <c r="M28" s="2">
         <f t="shared" si="4"/>
-        <v>554125.21679320722</v>
+        <v>556906.99370220723</v>
       </c>
       <c r="N28" s="5">
         <f t="shared" si="1"/>
-        <v>587372.72980079963</v>
+        <v>590321.41332433966</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -5048,7 +5075,7 @@
       </c>
       <c r="J29" s="19">
         <f t="shared" si="2"/>
-        <v>102621.88229999998</v>
+        <v>105403.65920899996</v>
       </c>
       <c r="K29" s="19">
         <f t="shared" si="3"/>
@@ -5057,11 +5084,11 @@
       <c r="L29" s="88"/>
       <c r="M29" s="2">
         <f t="shared" si="4"/>
-        <v>555055.4884941018</v>
+        <v>557837.2654031018</v>
       </c>
       <c r="N29" s="5">
         <f t="shared" si="1"/>
-        <v>588358.81780374795</v>
+        <v>591307.50132728787</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -5092,7 +5119,7 @@
       <c r="I30" s="32"/>
       <c r="J30" s="19">
         <f t="shared" si="2"/>
-        <v>9408.4578000000001</v>
+        <v>9663.4933739999979</v>
       </c>
       <c r="K30" s="19">
         <f t="shared" si="3"/>
@@ -5101,11 +5128,11 @@
       <c r="L30" s="88"/>
       <c r="M30" s="2">
         <f t="shared" si="4"/>
-        <v>50920.41780000001</v>
+        <v>51175.453374000004</v>
       </c>
       <c r="N30" s="5">
         <f t="shared" si="1"/>
-        <v>53975.64286800001</v>
+        <v>54245.980576440008</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -5136,7 +5163,7 @@
       <c r="I31" s="32"/>
       <c r="J31" s="19">
         <f t="shared" si="2"/>
-        <v>9582.6885000000002</v>
+        <v>9842.4469549999994</v>
       </c>
       <c r="K31" s="19">
         <f t="shared" si="3"/>
@@ -5145,11 +5172,11 @@
       <c r="L31" s="88"/>
       <c r="M31" s="2">
         <f t="shared" si="4"/>
-        <v>51863.388500000001</v>
+        <v>52123.146954999997</v>
       </c>
       <c r="N31" s="5">
         <f t="shared" si="1"/>
-        <v>54975.191810000004</v>
+        <v>55250.535772299998</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -5180,7 +5207,7 @@
       <c r="I32" s="32"/>
       <c r="J32" s="19">
         <f t="shared" si="2"/>
-        <v>7840.3815000000013</v>
+        <v>8052.9111449999991</v>
       </c>
       <c r="K32" s="19">
         <f t="shared" si="3"/>
@@ -5189,11 +5216,11 @@
       <c r="L32" s="68"/>
       <c r="M32" s="2">
         <f t="shared" si="4"/>
-        <v>42433.681500000006</v>
+        <v>42646.211145000001</v>
       </c>
       <c r="N32" s="5">
         <f t="shared" si="1"/>
-        <v>44979.702390000006</v>
+        <v>45204.983813700004</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -5224,7 +5251,7 @@
       <c r="I33" s="32"/>
       <c r="J33" s="19">
         <f t="shared" si="2"/>
-        <v>10628.072699999999</v>
+        <v>10916.168440999996</v>
       </c>
       <c r="K33" s="19">
         <f t="shared" si="3"/>
@@ -5233,11 +5260,11 @@
       <c r="L33" s="68"/>
       <c r="M33" s="2">
         <f t="shared" si="4"/>
-        <v>57521.212699999996</v>
+        <v>57809.308440999994</v>
       </c>
       <c r="N33" s="5">
         <f t="shared" si="1"/>
-        <v>60972.485461999997</v>
+        <v>61277.866947459996</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -5268,7 +5295,7 @@
       <c r="I34" s="32"/>
       <c r="J34" s="19">
         <f t="shared" si="2"/>
-        <v>9408.4578000000001</v>
+        <v>9663.4933739999979</v>
       </c>
       <c r="K34" s="19">
         <f t="shared" si="3"/>
@@ -5277,11 +5304,11 @@
       <c r="L34" s="68"/>
       <c r="M34" s="2">
         <f t="shared" si="4"/>
-        <v>50920.41780000001</v>
+        <v>51175.453374000004</v>
       </c>
       <c r="N34" s="5">
         <f t="shared" si="1"/>
-        <v>53975.64286800001</v>
+        <v>54245.980576440008</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -5298,7 +5325,7 @@
       <c r="E35" s="3">
         <v>0.5</v>
       </c>
-      <c r="F35" s="214">
+      <c r="F35" s="160">
         <v>80937</v>
       </c>
       <c r="G35" s="105">
@@ -5312,7 +5339,7 @@
       <c r="I35" s="32"/>
       <c r="J35" s="19">
         <f t="shared" si="2"/>
-        <v>8711.5349999999999</v>
+        <v>8947.6790499999988</v>
       </c>
       <c r="K35" s="19">
         <f t="shared" si="3"/>
@@ -5321,11 +5348,11 @@
       <c r="L35" s="68"/>
       <c r="M35" s="2">
         <f t="shared" si="4"/>
-        <v>47148.535000000003</v>
+        <v>47384.679049999999</v>
       </c>
       <c r="N35" s="5">
         <f t="shared" si="1"/>
-        <v>49977.447100000005</v>
+        <v>50227.759792999997</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -5356,7 +5383,7 @@
       <c r="I36" s="32"/>
       <c r="J36" s="19">
         <f t="shared" si="2"/>
-        <v>8711.5349999999999</v>
+        <v>8947.6790499999988</v>
       </c>
       <c r="K36" s="19">
         <f t="shared" si="3"/>
@@ -5365,11 +5392,11 @@
       <c r="L36" s="68"/>
       <c r="M36" s="2">
         <f t="shared" si="4"/>
-        <v>47148.535000000003</v>
+        <v>47384.679049999999</v>
       </c>
       <c r="N36" s="5">
         <f t="shared" si="1"/>
-        <v>49977.447100000005</v>
+        <v>50227.759792999997</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -5400,7 +5427,7 @@
       <c r="I37" s="32"/>
       <c r="J37" s="19">
         <f t="shared" si="2"/>
-        <v>8537.3042999999998</v>
+        <v>8768.7254689999972</v>
       </c>
       <c r="K37" s="19">
         <f t="shared" si="3"/>
@@ -5409,11 +5436,11 @@
       <c r="L37" s="68"/>
       <c r="M37" s="2">
         <f t="shared" si="4"/>
-        <v>46205.564299999998</v>
+        <v>46436.985468999999</v>
       </c>
       <c r="N37" s="5">
         <f t="shared" si="1"/>
-        <v>48977.898157999996</v>
+        <v>49223.20459714</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -5444,7 +5471,7 @@
       <c r="I38" s="32"/>
       <c r="J38" s="19">
         <f t="shared" si="2"/>
-        <v>8537.3042999999998</v>
+        <v>8768.7254689999972</v>
       </c>
       <c r="K38" s="19">
         <f t="shared" si="3"/>
@@ -5453,11 +5480,11 @@
       <c r="L38" s="68"/>
       <c r="M38" s="2">
         <f t="shared" si="4"/>
-        <v>46205.564299999998</v>
+        <v>46436.985468999999</v>
       </c>
       <c r="N38" s="5">
         <f t="shared" si="1"/>
-        <v>48977.898157999996</v>
+        <v>49223.20459714</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -5488,7 +5515,7 @@
       <c r="I39" s="32"/>
       <c r="J39" s="19">
         <f t="shared" si="2"/>
-        <v>10279.6113</v>
+        <v>10558.261278999997</v>
       </c>
       <c r="K39" s="19">
         <f t="shared" si="3"/>
@@ -5497,11 +5524,11 @@
       <c r="L39" s="68"/>
       <c r="M39" s="2">
         <f t="shared" si="4"/>
-        <v>55635.271300000008</v>
+        <v>55913.921279000002</v>
       </c>
       <c r="N39" s="5">
         <f t="shared" si="1"/>
-        <v>58973.387578000009</v>
+        <v>59268.756555740001</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -5532,7 +5559,7 @@
       <c r="I40" s="32"/>
       <c r="J40" s="19">
         <f t="shared" si="2"/>
-        <v>9931.1498999999985</v>
+        <v>10200.354116999997</v>
       </c>
       <c r="K40" s="19">
         <f t="shared" si="3"/>
@@ -5541,11 +5568,11 @@
       <c r="L40" s="68"/>
       <c r="M40" s="2">
         <f t="shared" si="4"/>
-        <v>53749.329899999997</v>
+        <v>54018.534116999996</v>
       </c>
       <c r="N40" s="5">
         <f t="shared" si="1"/>
-        <v>56974.289693999999</v>
+        <v>57259.646164019992</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -5576,7 +5603,7 @@
       <c r="I41" s="32"/>
       <c r="J41" s="19">
         <f t="shared" si="2"/>
-        <v>9408.4578000000001</v>
+        <v>9663.4933739999979</v>
       </c>
       <c r="K41" s="19">
         <f t="shared" si="3"/>
@@ -5585,11 +5612,11 @@
       <c r="L41" s="68"/>
       <c r="M41" s="2">
         <f t="shared" si="4"/>
-        <v>50920.41780000001</v>
+        <v>51175.453374000004</v>
       </c>
       <c r="N41" s="5">
         <f t="shared" si="1"/>
-        <v>53975.64286800001</v>
+        <v>54245.980576440008</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -5620,7 +5647,7 @@
       <c r="I42" s="32"/>
       <c r="J42" s="19">
         <f t="shared" si="2"/>
-        <v>9582.6885000000002</v>
+        <v>9842.4469549999994</v>
       </c>
       <c r="K42" s="19">
         <f t="shared" si="3"/>
@@ -5629,11 +5656,11 @@
       <c r="L42" s="68"/>
       <c r="M42" s="2">
         <f t="shared" si="4"/>
-        <v>51863.388500000001</v>
+        <v>52123.146954999997</v>
       </c>
       <c r="N42" s="5">
         <f t="shared" si="1"/>
-        <v>54975.191810000004</v>
+        <v>55250.535772299998</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -5664,7 +5691,7 @@
       <c r="I43" s="32"/>
       <c r="J43" s="19">
         <f t="shared" si="2"/>
-        <v>7840.3815000000013</v>
+        <v>8052.9111449999991</v>
       </c>
       <c r="K43" s="19">
         <f t="shared" si="3"/>
@@ -5673,15 +5700,15 @@
       <c r="L43" s="68"/>
       <c r="M43" s="2">
         <f t="shared" si="4"/>
-        <v>42433.681500000006</v>
+        <v>42646.211145000001</v>
       </c>
       <c r="N43" s="5">
         <f t="shared" si="1"/>
-        <v>44979.702390000006</v>
+        <v>45204.983813700004</v>
       </c>
       <c r="P43" s="34">
         <f>L1-K52</f>
-        <v>1443769.6600420019</v>
+        <v>1443921.6600420019</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -5712,7 +5739,7 @@
       <c r="I44" s="32"/>
       <c r="J44" s="19">
         <f t="shared" si="2"/>
-        <v>10628.072699999999</v>
+        <v>10916.168440999996</v>
       </c>
       <c r="K44" s="19">
         <f t="shared" si="3"/>
@@ -5721,11 +5748,11 @@
       <c r="L44" s="68"/>
       <c r="M44" s="2">
         <f t="shared" si="4"/>
-        <v>57521.212699999996</v>
+        <v>57809.308440999994</v>
       </c>
       <c r="N44" s="5">
         <f t="shared" si="1"/>
-        <v>60972.485461999997</v>
+        <v>61277.866947459996</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -5756,7 +5783,7 @@
       <c r="I45" s="32"/>
       <c r="J45" s="19">
         <f t="shared" si="2"/>
-        <v>9408.4578000000001</v>
+        <v>9663.4933739999979</v>
       </c>
       <c r="K45" s="19">
         <f t="shared" si="3"/>
@@ -5765,11 +5792,11 @@
       <c r="L45" s="68"/>
       <c r="M45" s="2">
         <f t="shared" si="4"/>
-        <v>50920.41780000001</v>
+        <v>51175.453374000004</v>
       </c>
       <c r="N45" s="5">
         <f t="shared" si="1"/>
-        <v>53975.64286800001</v>
+        <v>54245.980576440008</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -5800,7 +5827,7 @@
       <c r="I46" s="32"/>
       <c r="J46" s="19">
         <f t="shared" si="2"/>
-        <v>8711.5349999999999</v>
+        <v>8947.6790499999988</v>
       </c>
       <c r="K46" s="19">
         <f t="shared" si="3"/>
@@ -5809,11 +5836,11 @@
       <c r="L46" s="68"/>
       <c r="M46" s="2">
         <f t="shared" si="4"/>
-        <v>47148.535000000003</v>
+        <v>47384.679049999999</v>
       </c>
       <c r="N46" s="5">
         <f t="shared" si="1"/>
-        <v>49977.447100000005</v>
+        <v>50227.759792999997</v>
       </c>
       <c r="Q46" t="s">
         <v>101</v>
@@ -5847,7 +5874,7 @@
       <c r="I47" s="32"/>
       <c r="J47" s="19">
         <f t="shared" si="2"/>
-        <v>8711.5349999999999</v>
+        <v>8947.6790499999988</v>
       </c>
       <c r="K47" s="19">
         <f t="shared" si="3"/>
@@ -5856,16 +5883,16 @@
       <c r="L47" s="68"/>
       <c r="M47" s="2">
         <f t="shared" si="4"/>
-        <v>47148.535000000003</v>
+        <v>47384.679049999999</v>
       </c>
       <c r="N47" s="5">
         <f t="shared" si="1"/>
-        <v>49977.447100000005</v>
+        <v>50227.759792999997</v>
       </c>
       <c r="O47" s="53"/>
       <c r="Q47" s="50">
         <f>M3-J52</f>
-        <v>4883259.6363000013</v>
+        <v>4934309.2570290007</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -5896,7 +5923,7 @@
       <c r="I48" s="32"/>
       <c r="J48" s="19">
         <f t="shared" si="2"/>
-        <v>8537.3042999999998</v>
+        <v>8768.7254689999972</v>
       </c>
       <c r="K48" s="19">
         <f t="shared" si="3"/>
@@ -5905,11 +5932,11 @@
       <c r="L48" s="68"/>
       <c r="M48" s="2">
         <f t="shared" si="4"/>
-        <v>46205.564299999998</v>
+        <v>46436.985468999999</v>
       </c>
       <c r="N48" s="5">
         <f t="shared" si="1"/>
-        <v>48977.898157999996</v>
+        <v>49223.20459714</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -5941,7 +5968,7 @@
       <c r="I49" s="32"/>
       <c r="J49" s="19">
         <f t="shared" si="2"/>
-        <v>8537.3042999999998</v>
+        <v>8768.7254689999972</v>
       </c>
       <c r="K49" s="19">
         <f t="shared" si="3"/>
@@ -5950,11 +5977,11 @@
       <c r="L49" s="68"/>
       <c r="M49" s="2">
         <f t="shared" si="4"/>
-        <v>46205.564299999998</v>
+        <v>46436.985468999999</v>
       </c>
       <c r="N49" s="5">
         <f t="shared" si="1"/>
-        <v>48977.898157999996</v>
+        <v>49223.20459714</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -5985,7 +6012,7 @@
       <c r="I50" s="32"/>
       <c r="J50" s="19">
         <f t="shared" si="2"/>
-        <v>10279.6113</v>
+        <v>10558.261278999997</v>
       </c>
       <c r="K50" s="19">
         <f t="shared" si="3"/>
@@ -5994,11 +6021,11 @@
       <c r="L50" s="68"/>
       <c r="M50" s="2">
         <f t="shared" si="4"/>
-        <v>55635.271300000008</v>
+        <v>55913.921279000002</v>
       </c>
       <c r="N50" s="5">
         <f t="shared" si="1"/>
-        <v>58973.387578000009</v>
+        <v>59268.756555740001</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -6029,7 +6056,7 @@
       <c r="I51" s="32"/>
       <c r="J51" s="19">
         <f t="shared" si="2"/>
-        <v>9931.1498999999985</v>
+        <v>10200.354116999997</v>
       </c>
       <c r="K51" s="19">
         <f t="shared" si="3"/>
@@ -6038,11 +6065,11 @@
       <c r="L51" s="68"/>
       <c r="M51" s="2">
         <f t="shared" si="4"/>
-        <v>53749.329899999997</v>
+        <v>54018.534116999996</v>
       </c>
       <c r="N51" s="5">
         <f t="shared" si="1"/>
-        <v>56974.289693999999</v>
+        <v>57259.646164019992</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6066,7 +6093,7 @@
       <c r="I52" s="20"/>
       <c r="J52" s="45">
         <f>SUM(J8:J51)</f>
-        <v>1601354.3636999985</v>
+        <v>1644762.3629709994</v>
       </c>
       <c r="K52" s="21">
         <f>SUM(K7:K51)</f>
@@ -6078,47 +6105,47 @@
       </c>
       <c r="M52" s="22">
         <f>SUM(M7:M51)</f>
-        <v>6428977.0237200372</v>
+        <v>6476205.8337200405</v>
       </c>
       <c r="N52" s="21">
         <f>SUM(N7:N51)</f>
-        <v>6814715.6451432398</v>
+        <v>6864778.1837432366</v>
       </c>
       <c r="P52" s="50"/>
     </row>
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="53">
         <f>K52-L1</f>
-        <v>-1443769.6600420019</v>
+        <v>-1443921.6600420019</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="211"/>
-      <c r="D54" s="211"/>
-      <c r="E54" s="211"/>
-      <c r="F54" s="211"/>
-      <c r="G54" s="211"/>
-      <c r="H54" s="211"/>
-      <c r="I54" s="211"/>
-      <c r="J54" s="211"/>
-      <c r="K54" s="211"/>
-      <c r="L54" s="211"/>
-      <c r="M54" s="211"/>
-      <c r="N54" s="211"/>
+      <c r="C54" s="193"/>
+      <c r="D54" s="193"/>
+      <c r="E54" s="193"/>
+      <c r="F54" s="193"/>
+      <c r="G54" s="193"/>
+      <c r="H54" s="193"/>
+      <c r="I54" s="193"/>
+      <c r="J54" s="193"/>
+      <c r="K54" s="193"/>
+      <c r="L54" s="193"/>
+      <c r="M54" s="193"/>
+      <c r="N54" s="193"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="211"/>
-      <c r="D55" s="211"/>
-      <c r="E55" s="211"/>
-      <c r="F55" s="211"/>
-      <c r="G55" s="211"/>
-      <c r="H55" s="211"/>
-      <c r="I55" s="211"/>
-      <c r="J55" s="211"/>
-      <c r="K55" s="211"/>
-      <c r="L55" s="211"/>
-      <c r="M55" s="211"/>
-      <c r="N55" s="211"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
+      <c r="E55" s="193"/>
+      <c r="F55" s="193"/>
+      <c r="G55" s="193"/>
+      <c r="H55" s="193"/>
+      <c r="I55" s="193"/>
+      <c r="J55" s="193"/>
+      <c r="K55" s="193"/>
+      <c r="L55" s="193"/>
+      <c r="M55" s="193"/>
+      <c r="N55" s="193"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="70"/>
@@ -6135,107 +6162,109 @@
       <c r="N56" s="70"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="211" t="s">
+      <c r="C57" s="193" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="211"/>
-      <c r="E57" s="211"/>
-      <c r="F57" s="211"/>
-      <c r="G57" s="211"/>
-      <c r="H57" s="211"/>
-      <c r="I57" s="211"/>
-      <c r="J57" s="211"/>
-      <c r="K57" s="211"/>
-      <c r="L57" s="211"/>
-      <c r="M57" s="211"/>
-      <c r="N57" s="211"/>
+      <c r="D57" s="193"/>
+      <c r="E57" s="193"/>
+      <c r="F57" s="193"/>
+      <c r="G57" s="193"/>
+      <c r="H57" s="193"/>
+      <c r="I57" s="193"/>
+      <c r="J57" s="193"/>
+      <c r="K57" s="193"/>
+      <c r="L57" s="193"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="193"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="211"/>
-      <c r="D58" s="211"/>
-      <c r="E58" s="211"/>
-      <c r="F58" s="211"/>
-      <c r="G58" s="211"/>
-      <c r="H58" s="211"/>
-      <c r="I58" s="211"/>
-      <c r="J58" s="211"/>
-      <c r="K58" s="211"/>
-      <c r="L58" s="211"/>
-      <c r="M58" s="211"/>
-      <c r="N58" s="211"/>
+      <c r="C58" s="193"/>
+      <c r="D58" s="193"/>
+      <c r="E58" s="193"/>
+      <c r="F58" s="193"/>
+      <c r="G58" s="193"/>
+      <c r="H58" s="193"/>
+      <c r="I58" s="193"/>
+      <c r="J58" s="193"/>
+      <c r="K58" s="193"/>
+      <c r="L58" s="193"/>
+      <c r="M58" s="193"/>
+      <c r="N58" s="193"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="211"/>
-      <c r="D59" s="211"/>
-      <c r="E59" s="211"/>
-      <c r="F59" s="211"/>
-      <c r="G59" s="211"/>
-      <c r="H59" s="211"/>
-      <c r="I59" s="211"/>
-      <c r="J59" s="211"/>
-      <c r="K59" s="211"/>
-      <c r="L59" s="211"/>
-      <c r="M59" s="211"/>
-      <c r="N59" s="211"/>
+      <c r="C59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="193"/>
+      <c r="L59" s="193"/>
+      <c r="M59" s="193"/>
+      <c r="N59" s="193"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="211"/>
-      <c r="D60" s="211"/>
-      <c r="E60" s="211"/>
-      <c r="F60" s="211"/>
-      <c r="G60" s="211"/>
-      <c r="H60" s="211"/>
-      <c r="I60" s="211"/>
-      <c r="J60" s="211"/>
-      <c r="K60" s="211"/>
-      <c r="L60" s="211"/>
-      <c r="M60" s="211"/>
-      <c r="N60" s="211"/>
+      <c r="C60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="193"/>
+      <c r="L60" s="193"/>
+      <c r="M60" s="193"/>
+      <c r="N60" s="193"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="211"/>
-      <c r="D61" s="211"/>
-      <c r="E61" s="211"/>
-      <c r="F61" s="211"/>
-      <c r="G61" s="211"/>
-      <c r="H61" s="211"/>
-      <c r="I61" s="211"/>
-      <c r="J61" s="211"/>
-      <c r="K61" s="211"/>
-      <c r="L61" s="211"/>
-      <c r="M61" s="211"/>
-      <c r="N61" s="211"/>
+      <c r="C61" s="193"/>
+      <c r="D61" s="193"/>
+      <c r="E61" s="193"/>
+      <c r="F61" s="193"/>
+      <c r="G61" s="193"/>
+      <c r="H61" s="193"/>
+      <c r="I61" s="193"/>
+      <c r="J61" s="193"/>
+      <c r="K61" s="193"/>
+      <c r="L61" s="193"/>
+      <c r="M61" s="193"/>
+      <c r="N61" s="193"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="211"/>
-      <c r="D62" s="211"/>
-      <c r="E62" s="211"/>
-      <c r="F62" s="211"/>
-      <c r="G62" s="211"/>
-      <c r="H62" s="211"/>
-      <c r="I62" s="211"/>
-      <c r="J62" s="211"/>
-      <c r="K62" s="211"/>
-      <c r="L62" s="211"/>
-      <c r="M62" s="211"/>
-      <c r="N62" s="211"/>
+      <c r="C62" s="193"/>
+      <c r="D62" s="193"/>
+      <c r="E62" s="193"/>
+      <c r="F62" s="193"/>
+      <c r="G62" s="193"/>
+      <c r="H62" s="193"/>
+      <c r="I62" s="193"/>
+      <c r="J62" s="193"/>
+      <c r="K62" s="193"/>
+      <c r="L62" s="193"/>
+      <c r="M62" s="193"/>
+      <c r="N62" s="193"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="211"/>
-      <c r="D63" s="211"/>
-      <c r="E63" s="211"/>
-      <c r="F63" s="211"/>
-      <c r="G63" s="211"/>
-      <c r="H63" s="211"/>
-      <c r="I63" s="211"/>
-      <c r="J63" s="211"/>
-      <c r="K63" s="211"/>
-      <c r="L63" s="211"/>
-      <c r="M63" s="211"/>
-      <c r="N63" s="211"/>
+      <c r="C63" s="193"/>
+      <c r="D63" s="193"/>
+      <c r="E63" s="193"/>
+      <c r="F63" s="193"/>
+      <c r="G63" s="193"/>
+      <c r="H63" s="193"/>
+      <c r="I63" s="193"/>
+      <c r="J63" s="193"/>
+      <c r="K63" s="193"/>
+      <c r="L63" s="193"/>
+      <c r="M63" s="193"/>
+      <c r="N63" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
@@ -6252,8 +6281,6 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/2026/BELGRANO 1646/Junio/Junio-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Junio/Junio-BLG1646.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54AD4A1-8BFF-45F4-8673-3A09B3E60513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB611F89-F041-4B8D-AF86-891F1C80B258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1388,6 +1388,12 @@
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1402,12 +1408,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3855,7 +3855,7 @@
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
     <col min="5" max="5" width="6.140625" customWidth="1"/>
     <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.140625" customWidth="1"/>
@@ -3887,11 +3887,11 @@
       <c r="K1" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="194">
+      <c r="L1" s="196">
         <f>RESUMEN!D88</f>
         <v>8819834.2200000007</v>
       </c>
-      <c r="M1" s="195"/>
+      <c r="M1" s="197"/>
       <c r="N1" s="91"/>
       <c r="O1" s="50">
         <f>L1*8.09%</f>
@@ -3970,25 +3970,25 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="198" t="s">
+      <c r="A5" s="193" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="214" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="198" t="s">
+      <c r="C5" s="193" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="203" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="198" t="s">
+      <c r="E5" s="193" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="198" t="s">
+      <c r="F5" s="193" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="198" t="s">
+      <c r="G5" s="193" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="200" t="s">
@@ -3997,37 +3997,37 @@
       <c r="I5" s="203" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="196" t="s">
+      <c r="K5" s="198" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="196" t="s">
+      <c r="L5" s="198" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="196" t="s">
+      <c r="M5" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="196" t="s">
+      <c r="N5" s="198" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="199"/>
+      <c r="A6" s="194"/>
       <c r="B6" s="215"/>
-      <c r="C6" s="199"/>
+      <c r="C6" s="194"/>
       <c r="D6" s="216"/>
-      <c r="E6" s="199"/>
-      <c r="F6" s="199"/>
-      <c r="G6" s="199"/>
+      <c r="E6" s="194"/>
+      <c r="F6" s="194"/>
+      <c r="G6" s="194"/>
       <c r="H6" s="201"/>
       <c r="I6" s="204"/>
       <c r="J6" s="202"/>
-      <c r="K6" s="197"/>
+      <c r="K6" s="199"/>
       <c r="L6" s="202"/>
-      <c r="M6" s="197"/>
-      <c r="N6" s="197"/>
+      <c r="M6" s="199"/>
+      <c r="N6" s="199"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -6120,32 +6120,32 @@
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="193"/>
-      <c r="D54" s="193"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
-      <c r="G54" s="193"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="193"/>
-      <c r="K54" s="193"/>
-      <c r="L54" s="193"/>
-      <c r="M54" s="193"/>
-      <c r="N54" s="193"/>
+      <c r="C54" s="195"/>
+      <c r="D54" s="195"/>
+      <c r="E54" s="195"/>
+      <c r="F54" s="195"/>
+      <c r="G54" s="195"/>
+      <c r="H54" s="195"/>
+      <c r="I54" s="195"/>
+      <c r="J54" s="195"/>
+      <c r="K54" s="195"/>
+      <c r="L54" s="195"/>
+      <c r="M54" s="195"/>
+      <c r="N54" s="195"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
-      <c r="M55" s="193"/>
-      <c r="N55" s="193"/>
+      <c r="C55" s="195"/>
+      <c r="D55" s="195"/>
+      <c r="E55" s="195"/>
+      <c r="F55" s="195"/>
+      <c r="G55" s="195"/>
+      <c r="H55" s="195"/>
+      <c r="I55" s="195"/>
+      <c r="J55" s="195"/>
+      <c r="K55" s="195"/>
+      <c r="L55" s="195"/>
+      <c r="M55" s="195"/>
+      <c r="N55" s="195"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="70"/>
@@ -6162,107 +6162,109 @@
       <c r="N56" s="70"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="193" t="s">
+      <c r="C57" s="195" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="193"/>
-      <c r="E57" s="193"/>
-      <c r="F57" s="193"/>
-      <c r="G57" s="193"/>
-      <c r="H57" s="193"/>
-      <c r="I57" s="193"/>
-      <c r="J57" s="193"/>
-      <c r="K57" s="193"/>
-      <c r="L57" s="193"/>
-      <c r="M57" s="193"/>
-      <c r="N57" s="193"/>
+      <c r="D57" s="195"/>
+      <c r="E57" s="195"/>
+      <c r="F57" s="195"/>
+      <c r="G57" s="195"/>
+      <c r="H57" s="195"/>
+      <c r="I57" s="195"/>
+      <c r="J57" s="195"/>
+      <c r="K57" s="195"/>
+      <c r="L57" s="195"/>
+      <c r="M57" s="195"/>
+      <c r="N57" s="195"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="193"/>
-      <c r="D58" s="193"/>
-      <c r="E58" s="193"/>
-      <c r="F58" s="193"/>
-      <c r="G58" s="193"/>
-      <c r="H58" s="193"/>
-      <c r="I58" s="193"/>
-      <c r="J58" s="193"/>
-      <c r="K58" s="193"/>
-      <c r="L58" s="193"/>
-      <c r="M58" s="193"/>
-      <c r="N58" s="193"/>
+      <c r="C58" s="195"/>
+      <c r="D58" s="195"/>
+      <c r="E58" s="195"/>
+      <c r="F58" s="195"/>
+      <c r="G58" s="195"/>
+      <c r="H58" s="195"/>
+      <c r="I58" s="195"/>
+      <c r="J58" s="195"/>
+      <c r="K58" s="195"/>
+      <c r="L58" s="195"/>
+      <c r="M58" s="195"/>
+      <c r="N58" s="195"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="193"/>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="193"/>
-      <c r="L59" s="193"/>
-      <c r="M59" s="193"/>
-      <c r="N59" s="193"/>
+      <c r="C59" s="195"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="195"/>
+      <c r="L59" s="195"/>
+      <c r="M59" s="195"/>
+      <c r="N59" s="195"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="193"/>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="193"/>
-      <c r="L60" s="193"/>
-      <c r="M60" s="193"/>
-      <c r="N60" s="193"/>
+      <c r="C60" s="195"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="195"/>
+      <c r="L60" s="195"/>
+      <c r="M60" s="195"/>
+      <c r="N60" s="195"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="193"/>
-      <c r="D61" s="193"/>
-      <c r="E61" s="193"/>
-      <c r="F61" s="193"/>
-      <c r="G61" s="193"/>
-      <c r="H61" s="193"/>
-      <c r="I61" s="193"/>
-      <c r="J61" s="193"/>
-      <c r="K61" s="193"/>
-      <c r="L61" s="193"/>
-      <c r="M61" s="193"/>
-      <c r="N61" s="193"/>
+      <c r="C61" s="195"/>
+      <c r="D61" s="195"/>
+      <c r="E61" s="195"/>
+      <c r="F61" s="195"/>
+      <c r="G61" s="195"/>
+      <c r="H61" s="195"/>
+      <c r="I61" s="195"/>
+      <c r="J61" s="195"/>
+      <c r="K61" s="195"/>
+      <c r="L61" s="195"/>
+      <c r="M61" s="195"/>
+      <c r="N61" s="195"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="193"/>
-      <c r="D62" s="193"/>
-      <c r="E62" s="193"/>
-      <c r="F62" s="193"/>
-      <c r="G62" s="193"/>
-      <c r="H62" s="193"/>
-      <c r="I62" s="193"/>
-      <c r="J62" s="193"/>
-      <c r="K62" s="193"/>
-      <c r="L62" s="193"/>
-      <c r="M62" s="193"/>
-      <c r="N62" s="193"/>
+      <c r="C62" s="195"/>
+      <c r="D62" s="195"/>
+      <c r="E62" s="195"/>
+      <c r="F62" s="195"/>
+      <c r="G62" s="195"/>
+      <c r="H62" s="195"/>
+      <c r="I62" s="195"/>
+      <c r="J62" s="195"/>
+      <c r="K62" s="195"/>
+      <c r="L62" s="195"/>
+      <c r="M62" s="195"/>
+      <c r="N62" s="195"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="193"/>
-      <c r="D63" s="193"/>
-      <c r="E63" s="193"/>
-      <c r="F63" s="193"/>
-      <c r="G63" s="193"/>
-      <c r="H63" s="193"/>
-      <c r="I63" s="193"/>
-      <c r="J63" s="193"/>
-      <c r="K63" s="193"/>
-      <c r="L63" s="193"/>
-      <c r="M63" s="193"/>
-      <c r="N63" s="193"/>
+      <c r="C63" s="195"/>
+      <c r="D63" s="195"/>
+      <c r="E63" s="195"/>
+      <c r="F63" s="195"/>
+      <c r="G63" s="195"/>
+      <c r="H63" s="195"/>
+      <c r="I63" s="195"/>
+      <c r="J63" s="195"/>
+      <c r="K63" s="195"/>
+      <c r="L63" s="195"/>
+      <c r="M63" s="195"/>
+      <c r="N63" s="195"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
@@ -6279,8 +6281,6 @@
     <mergeCell ref="A1:J4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
